--- a/baseline/data_processing_elements-NES.xlsx
+++ b/baseline/data_processing_elements-NES.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/849507f40a0f895e/Documents/ProPASS/NES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{DBD72419-52E8-4439-AB9B-D71018BC44AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74CD8DFF-3988-4156-B39C-AB883D5D7CDC}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{DBD72419-52E8-4439-AB9B-D71018BC44AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B1F98D7-3C1C-43A3-96D3-D44C78D7ED80}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
   </bookViews>
   <sheets>
     <sheet name="DPE" sheetId="1" r:id="rId1"/>
-    <sheet name="education ref" sheetId="3" r:id="rId2"/>
-    <sheet name="Updates" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DPE!$A$1:$AF$122</definedName>
@@ -44,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="897">
   <si>
     <t>index</t>
   </si>
@@ -1674,38 +1672,6 @@
 6= higher professional education (high);
 7= university (high);
 8= Other;
-. = missing</t>
-  </si>
-  <si>
-    <t>1= lower education (primary school) (low)
-	Primair onderwijs or Basisonderwijs
-	Primary education
-	ISCED 1
-2= lower pre-vocational education (low),  
-	VMBO Voorbereidend Middelbaar Beroepsonderwijs
-	Preparatory secondary vocational education 
-	ISCED 2
-3= pre-vocational education (moderate)
-	VMBO oorbereidend middelbaar beroepsonderwijs
-	Pre-vocational secondary education 
-	ISCED 2
-4= middle-level applied education (moderate)
-	MBO Middelbaar Beroepsonderwijs
-	Secondary vocational education (assistant, basic, professional, middle-management)
-	ISCED 3
-5= secondary education (moderate)
-	Voortgezet onderwijs: Voorbereidend Wetenschappelijk Onderwijs (VWO) or Hoger Algemeen Voortgezet Onderwijs (HAVO)
-	Secondary education
-	ISCED 2-3
-6= higher professional education (high)
-	Hoger beroepsonderwijs (HBO)
-	higher professional education
-	ISCED 5-7
-7= university (high), = ISCED 6-8
-	HBO bachelor, master, doctor
-	University
-	ISCED 6-8
-8= Other, 
 . = missing</t>
   </si>
   <si>
@@ -2748,18 +2714,6 @@
     <t>Confirm: are missing values considered to be no sports?</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Pending questions</t>
-  </si>
-  <si>
-    <t>Change from previous version</t>
-  </si>
-  <si>
     <t>No other populations indicated. Only one dataset. Ok for now.</t>
   </si>
   <si>
@@ -2777,18 +2731,6 @@
   </si>
   <si>
     <t>The algorithm should work, but I suggested a lubridate approach that's a little simpler and calculates years directly. The inputs are already texts in format YYYY-MM-DD.</t>
-  </si>
-  <si>
-    <t>Study dd</t>
-  </si>
-  <si>
-    <t>DataSchema</t>
-  </si>
-  <si>
-    <t>-Lts T-stroom  -Koninklijke Militaire School   (2 jaar) is gelijk gesteld aan MBO. ; 3-jarige HBS ; Conservatorium ; HBO+ 2 post-HBO's ; Lerarenopleiding Textiele werkvormen 2e graads [...]</t>
-  </si>
-  <si>
-    <t>Open text</t>
   </si>
   <si>
     <t>recode(1:3 = 0 ; 4:5 = 1 ; 6 = 2 ; 7 = 3 ; 8 = NA ; ELSE = NA)</t>
@@ -2973,12 +2915,6 @@
     <t>recode(
 1=1;
 ELSE=NA)</t>
-  </si>
-  <si>
-    <t>TW comments</t>
-  </si>
-  <si>
-    <t>To review harmo comments wording together at end.</t>
   </si>
   <si>
     <t>The study-specific variable for self-reported myocardial infarction was used to assign positive responses for the DataSchema variables. Negative responses could not be assigned.</t>
@@ -3433,7 +3369,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3466,12 +3402,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3489,7 +3419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3497,9 +3427,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3536,15 +3463,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3907,14 +3827,14 @@
     <col min="18" max="18" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="45.85546875" style="1" customWidth="1"/>
     <col min="20" max="20" width="17.28515625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="32.140625" style="15" customWidth="1"/>
+    <col min="21" max="21" width="32.140625" style="12" customWidth="1"/>
     <col min="22" max="22" width="15" style="1" customWidth="1"/>
     <col min="23" max="23" width="15.42578125" style="1" customWidth="1"/>
     <col min="24" max="24" width="16.140625" style="1" customWidth="1"/>
     <col min="25" max="25" width="49.7109375" style="2" customWidth="1"/>
     <col min="26" max="26" width="42.28515625" style="1" customWidth="1"/>
     <col min="27" max="27" width="46.42578125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="54.140625" style="17" customWidth="1"/>
+    <col min="28" max="28" width="54.140625" style="14" customWidth="1"/>
     <col min="29" max="29" width="39.140625" style="1" customWidth="1"/>
     <col min="30" max="30" width="29" style="1" customWidth="1"/>
     <col min="31" max="31" width="39.140625" style="1" customWidth="1"/>
@@ -3922,101 +3842,101 @@
     <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="T1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="16" t="s">
-        <v>855</v>
-      </c>
-      <c r="V1" s="13" t="s">
-        <v>856</v>
-      </c>
-      <c r="W1" s="13" t="s">
+      <c r="U1" s="13" t="s">
+        <v>844</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="W1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="13" t="s">
+      <c r="X1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="Z1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AA1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AB1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="13" t="s">
+      <c r="AC1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="13" t="s">
+      <c r="AD1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AE1" s="13" t="s">
+      <c r="AE1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AF1" s="13" t="s">
+      <c r="AF1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4025,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>28</v>
@@ -4072,14 +3992,14 @@
       <c r="Y2" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="AB2" s="15"/>
+      <c r="AB2" s="12"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>29</v>
@@ -4111,14 +4031,14 @@
       <c r="Y3" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="AB3" s="15"/>
+      <c r="AB3" s="12"/>
     </row>
     <row r="4" spans="1:32" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>30</v>
@@ -4153,8 +4073,8 @@
       <c r="Z4" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="AB4" s="15" t="s">
-        <v>780</v>
+      <c r="AB4" s="12" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -4162,7 +4082,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>31</v>
@@ -4194,14 +4114,14 @@
       <c r="Y5" s="2">
         <v>1</v>
       </c>
-      <c r="AB5" s="15"/>
+      <c r="AB5" s="12"/>
     </row>
     <row r="6" spans="1:32" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4224,7 +4144,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>484</v>
@@ -4250,17 +4170,17 @@
       <c r="W6" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X6" s="14" t="s">
-        <v>781</v>
+      <c r="X6" s="11" t="s">
+        <v>776</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="AA6" s="19" t="s">
-        <v>782</v>
-      </c>
-      <c r="AB6" s="15" t="s">
-        <v>783</v>
+        <v>776</v>
+      </c>
+      <c r="AA6" s="15" t="s">
+        <v>777</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="45" x14ac:dyDescent="0.25">
@@ -4268,7 +4188,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>33</v>
@@ -4313,7 +4233,7 @@
         <v>493</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="60" x14ac:dyDescent="0.25">
@@ -4321,7 +4241,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
@@ -4372,10 +4292,10 @@
         <v>486</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="AB8" s="15" t="s">
-        <v>785</v>
+        <v>779</v>
+      </c>
+      <c r="AB8" s="12" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="165" x14ac:dyDescent="0.25">
@@ -4383,7 +4303,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>35</v>
@@ -4425,16 +4345,16 @@
         <v>493</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="AA9" s="19" t="s">
-        <v>791</v>
-      </c>
-      <c r="AB9" s="15" t="s">
-        <v>798</v>
+        <v>506</v>
+      </c>
+      <c r="AA9" s="15" t="s">
+        <v>782</v>
+      </c>
+      <c r="AB9" s="12" t="s">
+        <v>789</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="135" x14ac:dyDescent="0.25">
@@ -4442,7 +4362,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>36</v>
@@ -4484,13 +4404,13 @@
         <v>493</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="AB10" s="15" t="s">
-        <v>861</v>
+        <v>507</v>
+      </c>
+      <c r="AB10" s="12" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4498,7 +4418,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>37</v>
@@ -4522,27 +4442,27 @@
         <v>446</v>
       </c>
       <c r="L11" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="U11" s="15" t="s">
-        <v>793</v>
-      </c>
-      <c r="V11" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="U11" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="V11" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W11" s="1" t="s">
@@ -4552,13 +4472,13 @@
         <v>493</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>876</v>
-      </c>
-      <c r="AB11" s="15" t="s">
-        <v>857</v>
+        <v>783</v>
+      </c>
+      <c r="AA11" s="15" t="s">
+        <v>865</v>
+      </c>
+      <c r="AB11" s="12" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4566,7 +4486,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>38</v>
@@ -4590,27 +4510,27 @@
         <v>446</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="U12" s="15" t="s">
-        <v>793</v>
-      </c>
-      <c r="V12" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="U12" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="V12" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W12" s="1" t="s">
@@ -4620,13 +4540,13 @@
         <v>493</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="AA12" s="19" t="s">
-        <v>876</v>
-      </c>
-      <c r="AB12" s="15" t="s">
-        <v>799</v>
+        <v>785</v>
+      </c>
+      <c r="AA12" s="15" t="s">
+        <v>865</v>
+      </c>
+      <c r="AB12" s="12" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4634,7 +4554,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>39</v>
@@ -4658,37 +4578,37 @@
         <v>446</v>
       </c>
       <c r="L13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S13" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W13" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="U13" s="15" t="s">
-        <v>859</v>
-      </c>
-      <c r="V13" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="X13" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4696,7 +4616,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>40</v>
@@ -4720,27 +4640,27 @@
         <v>446</v>
       </c>
       <c r="L14" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="U14" s="15" t="s">
-        <v>793</v>
-      </c>
-      <c r="V14" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="U14" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="V14" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W14" s="1" t="s">
@@ -4750,13 +4670,13 @@
         <v>493</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="AA14" s="19" t="s">
-        <v>876</v>
-      </c>
-      <c r="AB14" s="15" t="s">
-        <v>799</v>
+        <v>786</v>
+      </c>
+      <c r="AA14" s="15" t="s">
+        <v>865</v>
+      </c>
+      <c r="AB14" s="12" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4764,7 +4684,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>41</v>
@@ -4788,37 +4708,37 @@
         <v>446</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S15" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W15" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="U15" s="15" t="s">
-        <v>859</v>
-      </c>
-      <c r="V15" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="X15" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4826,7 +4746,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>42</v>
@@ -4850,37 +4770,37 @@
         <v>446</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S16" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W16" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="U16" s="15" t="s">
-        <v>859</v>
-      </c>
-      <c r="V16" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="X16" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -4888,7 +4808,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>43</v>
@@ -4912,37 +4832,37 @@
         <v>446</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S17" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W17" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="U17" s="15" t="s">
-        <v>859</v>
-      </c>
-      <c r="V17" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="X17" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -4950,7 +4870,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>44</v>
@@ -4974,37 +4894,37 @@
         <v>446</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S18" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="U18" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W18" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="U18" s="15" t="s">
-        <v>859</v>
-      </c>
-      <c r="V18" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>514</v>
-      </c>
       <c r="X18" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5012,7 +4932,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>45</v>
@@ -5036,27 +4956,27 @@
         <v>446</v>
       </c>
       <c r="L19" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="U19" s="15" t="s">
-        <v>860</v>
-      </c>
-      <c r="V19" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="U19" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="V19" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W19" s="1" t="s">
@@ -5066,13 +4986,13 @@
         <v>493</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA19" s="19" t="s">
-        <v>876</v>
-      </c>
-      <c r="AB19" s="15" t="s">
-        <v>800</v>
+        <v>515</v>
+      </c>
+      <c r="AA19" s="15" t="s">
+        <v>865</v>
+      </c>
+      <c r="AB19" s="12" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -5080,7 +5000,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>46</v>
@@ -5101,22 +5021,22 @@
         <v>447</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="O20" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>474</v>
@@ -5128,7 +5048,7 @@
         <v>493</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5136,7 +5056,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>47</v>
@@ -5156,17 +5076,17 @@
       <c r="K21" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="L21" s="17" t="s">
-        <v>796</v>
+      <c r="L21" s="14" t="s">
+        <v>787</v>
       </c>
       <c r="M21" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>472</v>
@@ -5175,7 +5095,7 @@
         <v>482</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>474</v>
@@ -5184,16 +5104,16 @@
         <v>501</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="AB21" s="15" t="s">
-        <v>862</v>
+        <v>560</v>
+      </c>
+      <c r="AB21" s="12" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -5201,7 +5121,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>48</v>
@@ -5219,16 +5139,16 @@
         <v>355</v>
       </c>
       <c r="L22" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="M22" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>472</v>
@@ -5237,7 +5157,7 @@
         <v>482</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>474</v>
@@ -5246,13 +5166,13 @@
         <v>475</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB22" s="15" t="s">
-        <v>889</v>
+        <v>776</v>
+      </c>
+      <c r="AB22" s="12" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="180" x14ac:dyDescent="0.25">
@@ -5260,7 +5180,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
@@ -5275,40 +5195,40 @@
         <v>349</v>
       </c>
       <c r="L23" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="W23" s="14" t="s">
+      <c r="W23" s="11" t="s">
         <v>501</v>
       </c>
       <c r="X23" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="AB23" s="15" t="s">
-        <v>802</v>
+        <v>533</v>
+      </c>
+      <c r="AB23" s="12" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5316,7 +5236,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -5337,22 +5257,22 @@
         <v>449</v>
       </c>
       <c r="L24" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="M24" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="S24" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>474</v>
@@ -5361,16 +5281,16 @@
         <v>501</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="AB24" s="15" t="s">
-        <v>810</v>
+        <v>540</v>
+      </c>
+      <c r="AB24" s="12" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5378,7 +5298,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>51</v>
@@ -5396,22 +5316,22 @@
         <v>450</v>
       </c>
       <c r="L25" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="O25" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>474</v>
@@ -5423,7 +5343,7 @@
         <v>493</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -5431,7 +5351,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>52</v>
@@ -5455,16 +5375,16 @@
         <v>477</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5472,7 +5392,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>53</v>
@@ -5493,16 +5413,16 @@
         <v>411</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>174</v>
       </c>
       <c r="N27" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="O27" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>472</v>
@@ -5516,17 +5436,17 @@
       <c r="V27" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="W27" s="14" t="s">
+      <c r="W27" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="X27" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y27" s="15" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB27" s="15" t="s">
-        <v>803</v>
+      <c r="X27" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y27" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB27" s="12" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5534,7 +5454,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>54</v>
@@ -5552,16 +5472,16 @@
         <v>452</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>174</v>
       </c>
       <c r="N28" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>472</v>
@@ -5578,14 +5498,14 @@
       <c r="W28" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X28" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="Y28" s="15" t="s">
-        <v>804</v>
-      </c>
-      <c r="AB28" s="15" t="s">
-        <v>805</v>
+      <c r="X28" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="Y28" s="12" t="s">
+        <v>795</v>
+      </c>
+      <c r="AB28" s="12" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -5593,7 +5513,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>55</v>
@@ -5614,16 +5534,16 @@
         <v>411</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>176</v>
       </c>
       <c r="N29" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>472</v>
@@ -5640,14 +5560,14 @@
       <c r="W29" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X29" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y29" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB29" s="15" t="s">
-        <v>806</v>
+      <c r="X29" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y29" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB29" s="12" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -5655,7 +5575,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>56</v>
@@ -5673,16 +5593,16 @@
         <v>452</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>176</v>
       </c>
       <c r="N30" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="O30" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>472</v>
@@ -5699,14 +5619,14 @@
       <c r="W30" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X30" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="Y30" s="15" t="s">
-        <v>807</v>
-      </c>
-      <c r="AB30" s="15" t="s">
-        <v>805</v>
+      <c r="X30" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="Y30" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="AB30" s="12" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="165" x14ac:dyDescent="0.25">
@@ -5714,7 +5634,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>57</v>
@@ -5735,25 +5655,25 @@
         <v>411</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="S31" s="2" t="s">
         <v>499</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>474</v>
@@ -5761,14 +5681,14 @@
       <c r="W31" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X31" s="14" t="s">
+      <c r="X31" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="Y31" s="15" t="s">
-        <v>808</v>
-      </c>
-      <c r="AB31" s="15" t="s">
-        <v>809</v>
+      <c r="Y31" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="AB31" s="12" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5776,7 +5696,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>58</v>
@@ -5797,16 +5717,16 @@
         <v>411</v>
       </c>
       <c r="L32" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="M32" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>472</v>
@@ -5823,14 +5743,14 @@
       <c r="W32" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X32" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y32" s="15" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB32" s="15" t="s">
-        <v>806</v>
+      <c r="X32" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y32" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB32" s="12" t="s">
+        <v>797</v>
       </c>
     </row>
     <row r="33" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5838,7 +5758,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>59</v>
@@ -5856,16 +5776,16 @@
         <v>452</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="M33" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="O33" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>472</v>
@@ -5882,17 +5802,17 @@
       <c r="W33" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X33" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="Y33" s="15" t="s">
-        <v>811</v>
+      <c r="X33" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="Y33" s="12" t="s">
+        <v>802</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="AB33" s="15" t="s">
-        <v>812</v>
+        <v>565</v>
+      </c>
+      <c r="AB33" s="12" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="34" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -5900,7 +5820,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>60</v>
@@ -5918,7 +5838,7 @@
         <v>359</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>474</v>
@@ -5930,7 +5850,7 @@
         <v>486</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="195" x14ac:dyDescent="0.25">
@@ -5938,7 +5858,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>61</v>
@@ -5953,7 +5873,7 @@
         <v>349</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>474</v>
@@ -5962,13 +5882,13 @@
         <v>501</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -5976,7 +5896,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>62</v>
@@ -5997,16 +5917,16 @@
         <v>412</v>
       </c>
       <c r="L36" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="M36" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="O36" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>472</v>
@@ -6017,8 +5937,8 @@
       <c r="T36" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="U36" s="15" t="s">
-        <v>863</v>
+      <c r="U36" s="12" t="s">
+        <v>852</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>474</v>
@@ -6026,17 +5946,17 @@
       <c r="W36" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X36" s="14" t="s">
+      <c r="X36" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="AB36" s="15" t="s">
-        <v>864</v>
+        <v>570</v>
+      </c>
+      <c r="AB36" s="12" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="37" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6044,7 +5964,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>63</v>
@@ -6065,16 +5985,16 @@
         <v>412</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="O37" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>575</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>472</v>
@@ -6085,8 +6005,8 @@
       <c r="T37" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="U37" s="15" t="s">
-        <v>863</v>
+      <c r="U37" s="12" t="s">
+        <v>852</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>474</v>
@@ -6094,17 +6014,17 @@
       <c r="W37" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X37" s="14" t="s">
+      <c r="X37" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="AB37" s="15" t="s">
-        <v>864</v>
+        <v>570</v>
+      </c>
+      <c r="AB37" s="12" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="38" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6112,7 +6032,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>64</v>
@@ -6133,16 +6053,16 @@
         <v>412</v>
       </c>
       <c r="L38" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="N38" s="1" t="s">
+      <c r="O38" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>472</v>
@@ -6151,10 +6071,10 @@
         <v>482</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="U38" s="15" t="s">
-        <v>863</v>
+        <v>578</v>
+      </c>
+      <c r="U38" s="12" t="s">
+        <v>852</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>474</v>
@@ -6162,17 +6082,17 @@
       <c r="W38" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X38" s="14" t="s">
+      <c r="X38" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="Y38" s="15" t="s">
-        <v>865</v>
+      <c r="Y38" s="12" t="s">
+        <v>854</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="AB38" s="15" t="s">
-        <v>864</v>
+        <v>570</v>
+      </c>
+      <c r="AB38" s="12" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -6180,7 +6100,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>65</v>
@@ -6204,19 +6124,19 @@
         <v>477</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="AB39" s="15" t="s">
-        <v>864</v>
+        <v>514</v>
+      </c>
+      <c r="AB39" s="12" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="40" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -6224,7 +6144,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>66</v>
@@ -6242,25 +6162,25 @@
         <v>453</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="O40" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="U40" s="15" t="s">
-        <v>866</v>
+        <v>584</v>
+      </c>
+      <c r="U40" s="12" t="s">
+        <v>855</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>474</v>
@@ -6271,15 +6191,15 @@
       <c r="X40" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="Y40" s="15" t="s">
-        <v>867</v>
+      <c r="Y40" s="12" t="s">
+        <v>856</v>
       </c>
       <c r="Z40" s="2"/>
-      <c r="AA40" s="19" t="s">
-        <v>868</v>
-      </c>
-      <c r="AB40" s="15" t="s">
-        <v>893</v>
+      <c r="AA40" s="15" t="s">
+        <v>857</v>
+      </c>
+      <c r="AB40" s="12" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
@@ -6287,7 +6207,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>67</v>
@@ -6308,16 +6228,16 @@
         <v>477</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
@@ -6325,7 +6245,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>68</v>
@@ -6346,16 +6266,16 @@
         <v>477</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6363,7 +6283,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>69</v>
@@ -6381,16 +6301,16 @@
         <v>365</v>
       </c>
       <c r="L43" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="M43" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="O43" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>472</v>
@@ -6399,7 +6319,7 @@
         <v>482</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>474</v>
@@ -6407,14 +6327,14 @@
       <c r="W43" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X43" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y43" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB43" s="15" t="s">
-        <v>869</v>
+      <c r="X43" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y43" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB43" s="12" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6422,7 +6342,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>70</v>
@@ -6440,16 +6360,16 @@
         <v>365</v>
       </c>
       <c r="L44" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="M44" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="O44" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>594</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>472</v>
@@ -6458,7 +6378,7 @@
         <v>482</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>474</v>
@@ -6466,14 +6386,14 @@
       <c r="W44" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X44" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y44" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB44" s="15" t="s">
-        <v>869</v>
+      <c r="X44" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y44" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB44" s="12" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6481,7 +6401,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>71</v>
@@ -6499,16 +6419,16 @@
         <v>365</v>
       </c>
       <c r="L45" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="M45" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="O45" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>472</v>
@@ -6517,7 +6437,7 @@
         <v>482</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>474</v>
@@ -6525,14 +6445,14 @@
       <c r="W45" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X45" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y45" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB45" s="15" t="s">
-        <v>869</v>
+      <c r="X45" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y45" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB45" s="12" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6540,7 +6460,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>72</v>
@@ -6561,16 +6481,16 @@
         <v>414</v>
       </c>
       <c r="L46" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="M46" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>601</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>602</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>472</v>
@@ -6579,7 +6499,7 @@
         <v>482</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="V46" s="1" t="s">
         <v>474</v>
@@ -6588,16 +6508,16 @@
         <v>501</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="AB46" s="15" t="s">
-        <v>870</v>
+        <v>602</v>
+      </c>
+      <c r="AB46" s="12" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6605,7 +6525,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>73</v>
@@ -6623,16 +6543,16 @@
         <v>365</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="M47" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="N47" s="1" t="s">
+      <c r="O47" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>472</v>
@@ -6641,7 +6561,7 @@
         <v>482</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="V47" s="1" t="s">
         <v>474</v>
@@ -6649,14 +6569,14 @@
       <c r="W47" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X47" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y47" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="AB47" s="15" t="s">
-        <v>869</v>
+      <c r="X47" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y47" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="AB47" s="12" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6664,7 +6584,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>74</v>
@@ -6682,19 +6602,19 @@
         <v>366</v>
       </c>
       <c r="L48" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="M48" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="N48" s="1" t="s">
+      <c r="O48" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="O48" s="2" t="s">
+      <c r="P48" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>612</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>472</v>
@@ -6703,7 +6623,7 @@
         <v>482</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="V48" s="1" t="s">
         <v>474</v>
@@ -6711,11 +6631,11 @@
       <c r="W48" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="X48" s="14" t="s">
-        <v>781</v>
-      </c>
-      <c r="Y48" s="14" t="s">
-        <v>781</v>
+      <c r="X48" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="Y48" s="11" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="49" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6723,7 +6643,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>75</v>
@@ -6747,16 +6667,16 @@
         <v>477</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="50" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6764,7 +6684,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>76</v>
@@ -6785,16 +6705,16 @@
         <v>477</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="51" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6802,7 +6722,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>77</v>
@@ -6826,16 +6746,16 @@
         <v>477</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X51" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="52" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6843,7 +6763,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>78</v>
@@ -6867,16 +6787,16 @@
         <v>477</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X52" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.25">
@@ -6884,7 +6804,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>79</v>
@@ -6905,16 +6825,16 @@
         <v>477</v>
       </c>
       <c r="V53" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="54" spans="1:28" ht="225" x14ac:dyDescent="0.25">
@@ -6922,7 +6842,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>80</v>
@@ -6942,30 +6862,30 @@
       <c r="I54" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="L54" s="15" t="s">
-        <v>815</v>
-      </c>
-      <c r="M54" s="15" t="s">
-        <v>816</v>
-      </c>
-      <c r="N54" s="15" t="s">
-        <v>817</v>
-      </c>
-      <c r="O54" s="15" t="s">
-        <v>818</v>
+      <c r="L54" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="M54" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>808</v>
+      </c>
+      <c r="O54" s="12" t="s">
+        <v>809</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>472</v>
       </c>
       <c r="S54" s="2"/>
       <c r="T54" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="U54" s="15" t="s">
         <v>614</v>
+      </c>
+      <c r="U54" s="12" t="s">
+        <v>613</v>
       </c>
       <c r="V54" s="1" t="s">
         <v>474</v>
@@ -6973,17 +6893,17 @@
       <c r="W54" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="X54" s="14" t="s">
+      <c r="X54" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="AB54" s="15" t="s">
-        <v>871</v>
+        <v>760</v>
+      </c>
+      <c r="AB54" s="12" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -6991,7 +6911,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>81</v>
@@ -7012,16 +6932,16 @@
         <v>477</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -7029,7 +6949,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>82</v>
@@ -7050,22 +6970,22 @@
         <v>456</v>
       </c>
       <c r="L56" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="M56" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="O56" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="R56" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>474</v>
@@ -7077,16 +6997,16 @@
         <v>493</v>
       </c>
       <c r="Y56" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="Z56" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="Z56" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="AA56" s="15" t="s">
-        <v>822</v>
-      </c>
-      <c r="AB56" s="15" t="s">
-        <v>821</v>
+      <c r="AA56" s="12" t="s">
+        <v>813</v>
+      </c>
+      <c r="AB56" s="12" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="57" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -7094,7 +7014,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>83</v>
@@ -7112,19 +7032,19 @@
         <v>457</v>
       </c>
       <c r="L57" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="N57" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="O57" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="N57" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>771</v>
-      </c>
       <c r="P57" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>472</v>
@@ -7133,26 +7053,26 @@
         <v>482</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="V57" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W57" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="X57" s="14" t="s">
-        <v>515</v>
+        <v>623</v>
+      </c>
+      <c r="V57" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W57" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="X57" s="11" t="s">
+        <v>514</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z57" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="AA57" s="17"/>
-      <c r="AB57" s="15" t="s">
-        <v>872</v>
+        <v>771</v>
+      </c>
+      <c r="AA57" s="14"/>
+      <c r="AB57" s="12" t="s">
+        <v>861</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -7160,7 +7080,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>84</v>
@@ -7181,19 +7101,19 @@
         <v>420</v>
       </c>
       <c r="L58" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="M58" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="N58" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="O58" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="N58" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="O58" s="2" t="s">
-        <v>771</v>
-      </c>
       <c r="P58" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>472</v>
@@ -7202,7 +7122,7 @@
         <v>482</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="V58" s="1" t="s">
         <v>474</v>
@@ -7214,13 +7134,13 @@
         <v>486</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="Z58" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="AB58" s="15" t="s">
-        <v>823</v>
+        <v>772</v>
+      </c>
+      <c r="AB58" s="12" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -7228,7 +7148,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>85</v>
@@ -7246,34 +7166,34 @@
         <v>355</v>
       </c>
       <c r="L59" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="M59" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="N59" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="N59" s="1" t="s">
+      <c r="O59" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="V59" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y59" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="60" spans="1:28" ht="165" x14ac:dyDescent="0.25">
@@ -7281,7 +7201,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>86</v>
@@ -7302,22 +7222,22 @@
         <v>458</v>
       </c>
       <c r="L60" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="M60" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="N60" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="O60" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="R60" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>474</v>
@@ -7326,13 +7246,13 @@
         <v>501</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="AB60" s="15" t="s">
-        <v>824</v>
+        <v>816</v>
+      </c>
+      <c r="AB60" s="12" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="61" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -7340,7 +7260,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>87</v>
@@ -7361,16 +7281,16 @@
         <v>477</v>
       </c>
       <c r="V61" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y61" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="62" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
@@ -7378,7 +7298,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>88</v>
@@ -7399,25 +7319,25 @@
         <v>460</v>
       </c>
       <c r="L62" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="M62" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="M62" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="N62" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="O62" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="Q62" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>634</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="V62" s="1" t="s">
         <v>474</v>
@@ -7426,16 +7346,16 @@
         <v>501</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="Y62" s="19" t="s">
-        <v>879</v>
+        <v>638</v>
+      </c>
+      <c r="Y62" s="15" t="s">
+        <v>868</v>
       </c>
       <c r="Z62" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="AB62" s="15" t="s">
-        <v>877</v>
+        <v>773</v>
+      </c>
+      <c r="AB62" s="12" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -7443,7 +7363,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>89</v>
@@ -7461,25 +7381,25 @@
         <v>460</v>
       </c>
       <c r="L63" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="M63" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="N63" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="N63" s="1" t="s">
+      <c r="O63" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="O63" s="2" t="s">
+      <c r="Q63" s="1" t="s">
         <v>633</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>634</v>
       </c>
       <c r="R63" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="V63" s="1" t="s">
         <v>474</v>
@@ -7488,13 +7408,13 @@
         <v>501</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y63" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="AB63" s="15" t="s">
-        <v>824</v>
+        <v>817</v>
+      </c>
+      <c r="AB63" s="12" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -7502,7 +7422,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>90</v>
@@ -7520,25 +7440,25 @@
         <v>460</v>
       </c>
       <c r="L64" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="M64" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="N64" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="O64" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="N64" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>638</v>
-      </c>
       <c r="Q64" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="V64" s="1" t="s">
         <v>474</v>
@@ -7547,13 +7467,13 @@
         <v>501</v>
       </c>
       <c r="X64" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="AB64" s="15" t="s">
-        <v>824</v>
+        <v>819</v>
+      </c>
+      <c r="AB64" s="12" t="s">
+        <v>815</v>
       </c>
     </row>
     <row r="65" spans="1:29" ht="180" x14ac:dyDescent="0.25">
@@ -7561,7 +7481,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>91</v>
@@ -7579,25 +7499,25 @@
         <v>461</v>
       </c>
       <c r="L65" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="M65" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="N65" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="N65" s="1" t="s">
+      <c r="O65" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="Q65" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R65" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="V65" s="1" t="s">
         <v>474</v>
@@ -7609,13 +7529,13 @@
         <v>493</v>
       </c>
       <c r="Y65" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="Z65" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="AB65" s="15" t="s">
-        <v>881</v>
+        <v>761</v>
+      </c>
+      <c r="AB65" s="12" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -7623,7 +7543,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>92</v>
@@ -7647,16 +7567,16 @@
         <v>477</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
@@ -7664,7 +7584,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>93</v>
@@ -7685,25 +7605,25 @@
         <v>460</v>
       </c>
       <c r="L67" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="M67" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="M67" s="2" t="s">
+      <c r="N67" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="N67" s="1" t="s">
+      <c r="O67" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="O67" s="2" t="s">
-        <v>650</v>
-      </c>
       <c r="Q67" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="V67" s="1" t="s">
         <v>474</v>
@@ -7712,16 +7632,16 @@
         <v>501</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="Y67" s="19" t="s">
-        <v>880</v>
+        <v>638</v>
+      </c>
+      <c r="Y67" s="15" t="s">
+        <v>869</v>
       </c>
       <c r="Z67" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="AB67" s="15" t="s">
-        <v>877</v>
+        <v>650</v>
+      </c>
+      <c r="AB67" s="12" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="255" x14ac:dyDescent="0.25">
@@ -7729,7 +7649,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>94</v>
@@ -7750,41 +7670,41 @@
         <v>422</v>
       </c>
       <c r="L68" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="M68" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="M68" s="2" t="s">
+      <c r="N68" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="O68" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>654</v>
-      </c>
       <c r="Q68" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="V68" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W68" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="X68" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="Y68" s="14" t="s">
-        <v>515</v>
+        <v>634</v>
+      </c>
+      <c r="V68" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W68" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="X68" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="Y68" s="11" t="s">
+        <v>514</v>
       </c>
       <c r="AA68" s="1"/>
-      <c r="AB68" s="15" t="s">
-        <v>882</v>
+      <c r="AB68" s="12" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="69" spans="1:29" ht="255" x14ac:dyDescent="0.25">
@@ -7792,7 +7712,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>95</v>
@@ -7810,40 +7730,40 @@
         <v>462</v>
       </c>
       <c r="L69" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="M69" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="N69" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="O69" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="N69" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="O69" s="2" t="s">
-        <v>654</v>
-      </c>
       <c r="Q69" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="V69" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W69" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="X69" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="Y69" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="AB69" s="15" t="s">
-        <v>882</v>
+        <v>634</v>
+      </c>
+      <c r="V69" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W69" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="X69" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="Y69" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="AB69" s="12" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7851,7 +7771,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>96</v>
@@ -7869,22 +7789,22 @@
         <v>463</v>
       </c>
       <c r="L70" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="M70" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="N70" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="O70" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="O70" s="2" t="s">
+      <c r="P70" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="P70" s="1" t="s">
+      <c r="Q70" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>660</v>
       </c>
       <c r="R70" s="1" t="s">
         <v>472</v>
@@ -7893,22 +7813,22 @@
         <v>482</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="V70" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="W70" s="14" t="s">
-        <v>514</v>
-      </c>
-      <c r="X70" s="14" t="s">
-        <v>515</v>
+        <v>660</v>
+      </c>
+      <c r="V70" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="W70" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="X70" s="11" t="s">
+        <v>514</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="AB70" s="15" t="s">
-        <v>827</v>
+        <v>514</v>
+      </c>
+      <c r="AB70" s="12" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="105" x14ac:dyDescent="0.25">
@@ -7916,7 +7836,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>97</v>
@@ -7934,22 +7854,22 @@
         <v>464</v>
       </c>
       <c r="L71" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="M71" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="M71" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="O71" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="U71" s="15" t="s">
-        <v>883</v>
+        <v>663</v>
+      </c>
+      <c r="U71" s="12" t="s">
+        <v>872</v>
       </c>
       <c r="V71" s="1" t="s">
         <v>474</v>
@@ -7961,13 +7881,13 @@
         <v>493</v>
       </c>
       <c r="Y71" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="Z71" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="Z71" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="AB71" s="1" t="s">
-        <v>885</v>
+        <v>874</v>
       </c>
     </row>
     <row r="72" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -7975,7 +7895,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>98</v>
@@ -7996,25 +7916,25 @@
         <v>446</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="M72" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="O72" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="N72" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="Q72" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="R72" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="U72" s="1"/>
       <c r="V72" s="1" t="s">
@@ -8027,19 +7947,19 @@
         <v>493</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="Z72" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AA72" s="2" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="AB72" s="2" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="AC72" s="1" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="120" x14ac:dyDescent="0.25">
@@ -8047,7 +7967,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>99</v>
@@ -8068,28 +7988,28 @@
         <v>446</v>
       </c>
       <c r="L73" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="M73" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="M73" s="2" t="s">
+      <c r="N73" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="N73" s="1" t="s">
+      <c r="O73" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="O73" s="2" t="s">
-        <v>674</v>
-      </c>
       <c r="Q73" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="U73" s="15" t="s">
-        <v>884</v>
+        <v>674</v>
+      </c>
+      <c r="U73" s="12" t="s">
+        <v>873</v>
       </c>
       <c r="V73" s="1" t="s">
         <v>474</v>
@@ -8098,13 +8018,13 @@
         <v>501</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y73" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="AB73" s="15" t="s">
-        <v>878</v>
+        <v>820</v>
+      </c>
+      <c r="AB73" s="12" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="405" x14ac:dyDescent="0.25">
@@ -8112,7 +8032,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>100</v>
@@ -8133,25 +8053,25 @@
         <v>446</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="M74" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="O74" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="N74" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>678</v>
-      </c>
       <c r="Q74" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="R74" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="V74" s="1" t="s">
         <v>474</v>
@@ -8160,19 +8080,19 @@
         <v>501</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="Z74" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AB74" s="2" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="AC74" s="1" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -8180,7 +8100,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>101</v>
@@ -8201,16 +8121,16 @@
         <v>477</v>
       </c>
       <c r="V75" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X75" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y75" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -8218,7 +8138,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>102</v>
@@ -8239,16 +8159,16 @@
         <v>477</v>
       </c>
       <c r="V76" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X76" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="77" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -8256,7 +8176,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>103</v>
@@ -8274,22 +8194,22 @@
         <v>465</v>
       </c>
       <c r="L77" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="M77" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="M77" s="2" t="s">
+      <c r="N77" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="O77" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="R77" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="V77" s="1" t="s">
         <v>474</v>
@@ -8301,7 +8221,7 @@
         <v>493</v>
       </c>
       <c r="Y77" s="2" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
     </row>
     <row r="78" spans="1:29" ht="210" x14ac:dyDescent="0.25">
@@ -8309,7 +8229,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>104</v>
@@ -8330,25 +8250,25 @@
         <v>466</v>
       </c>
       <c r="L78" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="N78" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="N78" s="1" t="s">
+      <c r="O78" s="2" t="s">
         <v>687</v>
-      </c>
-      <c r="O78" s="2" t="s">
-        <v>688</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="U78" s="15" t="s">
-        <v>690</v>
+        <v>520</v>
+      </c>
+      <c r="U78" s="12" t="s">
+        <v>689</v>
       </c>
       <c r="V78" s="1" t="s">
         <v>474</v>
@@ -8357,13 +8277,13 @@
         <v>501</v>
       </c>
       <c r="X78" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="Z78" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="150" x14ac:dyDescent="0.25">
@@ -8371,7 +8291,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>105</v>
@@ -8395,40 +8315,40 @@
         <v>466</v>
       </c>
       <c r="L79" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="M79" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="N79" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O79" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="N79" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S79" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="U79" s="15" t="s">
-        <v>834</v>
+        <v>520</v>
+      </c>
+      <c r="U79" s="12" t="s">
+        <v>823</v>
       </c>
       <c r="V79" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="W79" s="14" t="s">
+      <c r="W79" s="11" t="s">
         <v>501</v>
       </c>
       <c r="X79" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y79" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="AB79" s="15" t="s">
-        <v>888</v>
+        <v>822</v>
+      </c>
+      <c r="AB79" s="12" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="150" x14ac:dyDescent="0.25">
@@ -8436,7 +8356,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>106</v>
@@ -8460,22 +8380,22 @@
         <v>466</v>
       </c>
       <c r="L80" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="M80" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="M80" s="2" t="s">
+      <c r="N80" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O80" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S80" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V80" s="1" t="s">
         <v>474</v>
@@ -8487,7 +8407,7 @@
         <v>493</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="81" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8495,7 +8415,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>107</v>
@@ -8522,16 +8442,16 @@
         <v>477</v>
       </c>
       <c r="V81" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X81" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y81" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="82" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8539,7 +8459,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>108</v>
@@ -8563,22 +8483,22 @@
         <v>466</v>
       </c>
       <c r="L82" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="M82" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="M82" s="2" t="s">
+      <c r="N82" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O82" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>697</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S82" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V82" s="1" t="s">
         <v>474</v>
@@ -8590,7 +8510,7 @@
         <v>493</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="83" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8598,7 +8518,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>109</v>
@@ -8622,22 +8542,22 @@
         <v>466</v>
       </c>
       <c r="L83" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="M83" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="M83" s="2" t="s">
+      <c r="N83" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O83" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="R83" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V83" s="1" t="s">
         <v>474</v>
@@ -8649,7 +8569,7 @@
         <v>493</v>
       </c>
       <c r="Y83" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="84" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8657,7 +8577,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>110</v>
@@ -8681,22 +8601,22 @@
         <v>466</v>
       </c>
       <c r="L84" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="M84" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="M84" s="2" t="s">
+      <c r="N84" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O84" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O84" s="2" t="s">
-        <v>703</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S84" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V84" s="1" t="s">
         <v>474</v>
@@ -8708,7 +8628,7 @@
         <v>493</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85" spans="1:28" ht="195" x14ac:dyDescent="0.25">
@@ -8716,7 +8636,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>111</v>
@@ -8740,22 +8660,22 @@
         <v>466</v>
       </c>
       <c r="L85" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="M85" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="M85" s="2" t="s">
+      <c r="N85" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O85" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O85" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S85" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V85" s="1" t="s">
         <v>474</v>
@@ -8767,7 +8687,7 @@
         <v>493</v>
       </c>
       <c r="Y85" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="86" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8775,7 +8695,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>112</v>
@@ -8799,25 +8719,25 @@
         <v>466</v>
       </c>
       <c r="L86" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="M86" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="N86" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="N86" s="2" t="s">
+      <c r="O86" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="O86" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="U86" s="15" t="s">
-        <v>853</v>
+        <v>520</v>
+      </c>
+      <c r="U86" s="12" t="s">
+        <v>842</v>
       </c>
       <c r="V86" s="1" t="s">
         <v>474</v>
@@ -8826,16 +8746,16 @@
         <v>501</v>
       </c>
       <c r="X86" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="Z86" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="AB86" s="15" t="s">
-        <v>854</v>
+        <v>710</v>
+      </c>
+      <c r="AB86" s="12" t="s">
+        <v>843</v>
       </c>
     </row>
     <row r="87" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8843,7 +8763,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>113</v>
@@ -8867,25 +8787,25 @@
         <v>466</v>
       </c>
       <c r="L87" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="M87" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="M87" s="2" t="s">
+      <c r="N87" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O87" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S87" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="U87" s="15" t="s">
-        <v>715</v>
+        <v>520</v>
+      </c>
+      <c r="U87" s="12" t="s">
+        <v>714</v>
       </c>
       <c r="V87" s="1" t="s">
         <v>474</v>
@@ -8894,13 +8814,13 @@
         <v>501</v>
       </c>
       <c r="X87" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="AB87" s="15" t="s">
-        <v>836</v>
+        <v>824</v>
+      </c>
+      <c r="AB87" s="12" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="88" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8908,7 +8828,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>114</v>
@@ -8932,22 +8852,22 @@
         <v>466</v>
       </c>
       <c r="L88" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="M88" s="2" t="s">
+      <c r="N88" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O88" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S88" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V88" s="1" t="s">
         <v>474</v>
@@ -8959,7 +8879,7 @@
         <v>493</v>
       </c>
       <c r="Y88" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -8967,7 +8887,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>115</v>
@@ -8985,22 +8905,22 @@
         <v>467</v>
       </c>
       <c r="L89" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="M89" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="M89" s="2" t="s">
+      <c r="O89" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S89" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="U89" s="15" t="s">
-        <v>724</v>
+        <v>721</v>
+      </c>
+      <c r="U89" s="12" t="s">
+        <v>723</v>
       </c>
       <c r="V89" s="1" t="s">
         <v>474</v>
@@ -9012,7 +8932,7 @@
         <v>493</v>
       </c>
       <c r="Y89" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="90" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -9020,7 +8940,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>116</v>
@@ -9041,22 +8961,22 @@
         <v>466</v>
       </c>
       <c r="L90" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="M90" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="M90" s="2" t="s">
+      <c r="N90" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O90" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O90" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S90" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V90" s="1" t="s">
         <v>474</v>
@@ -9068,7 +8988,7 @@
         <v>493</v>
       </c>
       <c r="Y90" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="91" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9076,7 +8996,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>117</v>
@@ -9096,23 +9016,23 @@
       <c r="K91" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="L91" s="17" t="s">
-        <v>841</v>
+      <c r="L91" s="14" t="s">
+        <v>830</v>
       </c>
       <c r="M91" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N91" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R91" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V91" s="1" t="s">
         <v>474</v>
@@ -9121,16 +9041,16 @@
         <v>501</v>
       </c>
       <c r="X91" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y91" s="2" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="Z91" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="AB91" s="15" t="s">
-        <v>874</v>
+        <v>765</v>
+      </c>
+      <c r="AB91" s="12" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="92" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9138,7 +9058,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>118</v>
@@ -9159,22 +9079,22 @@
         <v>466</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="M92" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O92" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N92" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R92" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V92" s="1" t="s">
         <v>474</v>
@@ -9183,16 +9103,16 @@
         <v>501</v>
       </c>
       <c r="X92" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y92" s="2" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="Z92" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="AB92" s="15" t="s">
-        <v>874</v>
+        <v>765</v>
+      </c>
+      <c r="AB92" s="12" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="93" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9200,7 +9120,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>119</v>
@@ -9221,22 +9141,22 @@
         <v>466</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="M93" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O93" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O93" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S93" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V93" s="1" t="s">
         <v>474</v>
@@ -9245,16 +9165,16 @@
         <v>501</v>
       </c>
       <c r="X93" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y93" s="2" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="Z93" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="AB93" s="15" t="s">
-        <v>874</v>
+        <v>765</v>
+      </c>
+      <c r="AB93" s="12" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="94" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9262,7 +9182,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>120</v>
@@ -9283,25 +9203,25 @@
         <v>466</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M94" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O94" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R94" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="U94" s="15" t="s">
-        <v>842</v>
+        <v>727</v>
+      </c>
+      <c r="U94" s="12" t="s">
+        <v>831</v>
       </c>
       <c r="V94" s="1" t="s">
         <v>474</v>
@@ -9310,13 +9230,13 @@
         <v>501</v>
       </c>
       <c r="X94" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y94" s="2" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="Z94" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9324,7 +9244,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>121</v>
@@ -9348,16 +9268,16 @@
         <v>477</v>
       </c>
       <c r="V95" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z95" s="2"/>
     </row>
@@ -9366,7 +9286,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>122</v>
@@ -9390,16 +9310,16 @@
         <v>477</v>
       </c>
       <c r="V96" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X96" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z96" s="2"/>
     </row>
@@ -9408,7 +9328,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>123</v>
@@ -9432,16 +9352,16 @@
         <v>477</v>
       </c>
       <c r="V97" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z97" s="2"/>
     </row>
@@ -9450,7 +9370,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>124</v>
@@ -9471,22 +9391,22 @@
         <v>466</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="M98" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O98" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S98" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V98" s="1" t="s">
         <v>474</v>
@@ -9495,16 +9415,16 @@
         <v>501</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y98" s="2" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="Z98" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="AB98" s="15" t="s">
-        <v>874</v>
+        <v>728</v>
+      </c>
+      <c r="AB98" s="12" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="99" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9512,7 +9432,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>125</v>
@@ -9533,25 +9453,25 @@
         <v>466</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="M99" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O99" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O99" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S99" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="U99" s="15" t="s">
-        <v>846</v>
+        <v>727</v>
+      </c>
+      <c r="U99" s="12" t="s">
+        <v>835</v>
       </c>
       <c r="V99" s="1" t="s">
         <v>474</v>
@@ -9560,16 +9480,16 @@
         <v>501</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="Z99" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="AB99" s="15" t="s">
-        <v>875</v>
+        <v>734</v>
+      </c>
+      <c r="AB99" s="12" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="100" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9577,7 +9497,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>126</v>
@@ -9598,22 +9518,22 @@
         <v>466</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M100" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O100" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O100" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S100" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V100" s="1" t="s">
         <v>474</v>
@@ -9622,16 +9542,16 @@
         <v>501</v>
       </c>
       <c r="X100" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="Z100" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="AB100" s="15" t="s">
-        <v>874</v>
+        <v>728</v>
+      </c>
+      <c r="AB100" s="12" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="101" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9639,7 +9559,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>127</v>
@@ -9660,22 +9580,22 @@
         <v>466</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="M101" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O101" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O101" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V101" s="1" t="s">
         <v>474</v>
@@ -9684,16 +9604,16 @@
         <v>501</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y101" s="2" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="Z101" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="AB101" s="15" t="s">
-        <v>874</v>
+        <v>728</v>
+      </c>
+      <c r="AB101" s="12" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="102" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9701,7 +9621,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>128</v>
@@ -9725,16 +9645,16 @@
         <v>477</v>
       </c>
       <c r="V102" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z102" s="2"/>
     </row>
@@ -9743,7 +9663,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>129</v>
@@ -9764,22 +9684,22 @@
         <v>466</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="M103" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O103" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N103" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O103" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V103" s="1" t="s">
         <v>474</v>
@@ -9788,16 +9708,16 @@
         <v>501</v>
       </c>
       <c r="X103" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="Z103" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="AB103" s="15" t="s">
-        <v>874</v>
+        <v>728</v>
+      </c>
+      <c r="AB103" s="12" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="104" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9805,7 +9725,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>130</v>
@@ -9829,19 +9749,19 @@
         <v>477</v>
       </c>
       <c r="V104" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X104" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z104" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="105" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9849,7 +9769,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>131</v>
@@ -9873,19 +9793,19 @@
         <v>477</v>
       </c>
       <c r="V105" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X105" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z105" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="106" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9893,7 +9813,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>132</v>
@@ -9917,19 +9837,19 @@
         <v>477</v>
       </c>
       <c r="V106" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W106" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X106" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y106" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z106" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="107" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9937,7 +9857,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>133</v>
@@ -9961,19 +9881,19 @@
         <v>477</v>
       </c>
       <c r="V107" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X107" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y107" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Z107" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="108" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9981,7 +9901,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>134</v>
@@ -10002,22 +9922,22 @@
         <v>466</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="M108" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O108" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N108" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O108" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R108" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V108" s="1" t="s">
         <v>474</v>
@@ -10026,10 +9946,10 @@
         <v>501</v>
       </c>
       <c r="X108" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="Z108" s="2"/>
     </row>
@@ -10038,7 +9958,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>135</v>
@@ -10059,22 +9979,22 @@
         <v>466</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="M109" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O109" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="N109" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O109" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="V109" s="1" t="s">
         <v>474</v>
@@ -10083,10 +10003,10 @@
         <v>501</v>
       </c>
       <c r="X109" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y109" s="2" t="s">
-        <v>851</v>
+        <v>840</v>
       </c>
       <c r="Z109" s="2"/>
     </row>
@@ -10095,7 +10015,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>136</v>
@@ -10116,22 +10036,22 @@
         <v>466</v>
       </c>
       <c r="L110" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="M110" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="M110" s="2" t="s">
+      <c r="N110" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O110" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="N110" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O110" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="R110" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V110" s="1" t="s">
         <v>474</v>
@@ -10143,7 +10063,7 @@
         <v>493</v>
       </c>
       <c r="Y110" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="111" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10151,7 +10071,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>137</v>
@@ -10172,22 +10092,22 @@
         <v>466</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="M111" s="2" t="s">
         <v>258</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V111" s="1" t="s">
         <v>474</v>
@@ -10199,7 +10119,7 @@
         <v>493</v>
       </c>
       <c r="Y111" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="112" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10207,7 +10127,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>138</v>
@@ -10228,22 +10148,22 @@
         <v>466</v>
       </c>
       <c r="L112" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="M112" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="M112" s="2" t="s">
+      <c r="N112" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="O112" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="N112" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="O112" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S112" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V112" s="1" t="s">
         <v>474</v>
@@ -10255,7 +10175,7 @@
         <v>493</v>
       </c>
       <c r="Y112" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="113" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10263,7 +10183,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>139</v>
@@ -10284,22 +10204,22 @@
         <v>466</v>
       </c>
       <c r="L113" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="M113" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="M113" s="2" t="s">
+      <c r="N113" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="N113" s="1" t="s">
+      <c r="O113" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="O113" s="2" t="s">
-        <v>753</v>
       </c>
       <c r="R113" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V113" s="1" t="s">
         <v>474</v>
@@ -10311,10 +10231,10 @@
         <v>493</v>
       </c>
       <c r="Y113" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Z113" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="114" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10322,7 +10242,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>140</v>
@@ -10343,25 +10263,25 @@
         <v>466</v>
       </c>
       <c r="L114" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="M114" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="M114" s="2" t="s">
+      <c r="N114" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="O114" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="O114" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="U114" s="15" t="s">
-        <v>853</v>
+        <v>520</v>
+      </c>
+      <c r="U114" s="12" t="s">
+        <v>842</v>
       </c>
       <c r="V114" s="1" t="s">
         <v>474</v>
@@ -10373,13 +10293,13 @@
         <v>493</v>
       </c>
       <c r="Y114" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Z114" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="AB114" s="15" t="s">
-        <v>852</v>
+        <v>753</v>
+      </c>
+      <c r="AB114" s="12" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="115" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10387,7 +10307,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>141</v>
@@ -10408,25 +10328,25 @@
         <v>466</v>
       </c>
       <c r="L115" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="M115" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="M115" s="2" t="s">
+      <c r="N115" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="O115" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="N115" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="O115" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="U115" s="15" t="s">
-        <v>853</v>
+        <v>520</v>
+      </c>
+      <c r="U115" s="12" t="s">
+        <v>842</v>
       </c>
       <c r="V115" s="1" t="s">
         <v>474</v>
@@ -10438,13 +10358,13 @@
         <v>493</v>
       </c>
       <c r="Y115" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Z115" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="AB115" s="15" t="s">
-        <v>852</v>
+        <v>753</v>
+      </c>
+      <c r="AB115" s="12" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="116" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -10452,7 +10372,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>142</v>
@@ -10473,16 +10393,16 @@
         <v>477</v>
       </c>
       <c r="V116" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W116" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X116" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y116" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="117" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -10490,7 +10410,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>143</v>
@@ -10511,16 +10431,16 @@
         <v>477</v>
       </c>
       <c r="V117" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W117" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X117" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y117" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.25">
@@ -10528,7 +10448,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>144</v>
@@ -10549,16 +10469,16 @@
         <v>477</v>
       </c>
       <c r="V118" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W118" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X118" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y118" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="119" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10566,7 +10486,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>145</v>
@@ -10587,16 +10507,16 @@
         <v>477</v>
       </c>
       <c r="V119" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W119" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X119" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y119" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="120" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10604,7 +10524,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>146</v>
@@ -10625,16 +10545,16 @@
         <v>477</v>
       </c>
       <c r="V120" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W120" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X120" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y120" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="121" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10642,7 +10562,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>147</v>
@@ -10663,16 +10583,16 @@
         <v>477</v>
       </c>
       <c r="V121" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W121" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X121" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y121" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="122" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10680,7 +10600,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>148</v>
@@ -10701,16 +10621,16 @@
         <v>477</v>
       </c>
       <c r="V122" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W122" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X122" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Y122" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -10718,95 +10638,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D979CCE-8335-48C0-8C98-F16E7DE1FF2B}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="112" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="65.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>788</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E18BDE-6E0A-4305-BEE1-2D6B7F5E5C97}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>776</v>
-      </c>
-      <c r="B1" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
-        <v>832</v>
-      </c>
-      <c r="B5" s="21"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="20" t="s">
-        <v>833</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:B5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/baseline/data_processing_elements-NES.xlsx
+++ b/baseline/data_processing_elements-NES.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/849507f40a0f895e/Documents/ProPASS/NES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbtiali\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{DBD72419-52E8-4439-AB9B-D71018BC44AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B1F98D7-3C1C-43A3-96D3-D44C78D7ED80}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5098D060-15A2-4ADF-9F0C-4987B471B465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
   </bookViews>
@@ -2920,21 +2920,8 @@
     <t>The study-specific variable for self-reported myocardial infarction was used to assign positive responses for the DataSchema variables. Negative responses could not be assigned.</t>
   </si>
   <si>
-    <t>case_when(
-fq289 == 1 | fq319 == 1 | fq364 == 1 ~ 1L;
-fq289 == 0 &amp; fq319 == 0 &amp; fq364 ==0 ~ 0L ; 
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
     <t>I think the study variables cover all the options, so can assign 0 if all 0.
 Can remove as.numeric.</t>
-  </si>
-  <si>
-    <t>case_when(
-fq241 == 1 | fq244 == 1 ~ 1L;
-fq241 == 0 &amp; fq244 == 0 ~ 0L;
-fq241 == 0 | fq244 == 0 ~ 2L;
-ELSE ~ NA_integer_)</t>
   </si>
   <si>
     <t>case_when(
@@ -3326,6 +3313,19 @@
     <t>case_when(year(questionnaire_date) == 2021 &amp; !is.na(body_fat_mass_kg) &amp; body_fat_mass_kg &gt; 0 ~ "Single-frequency analysis (1500, Bodystat, Douglas, Isle of Man)";
 year(questionnaire_date) &gt; 2021 &amp; !is.na(body_fat_mass_kg) &amp; body_fat_mass_kg &gt; 0~ "multi-frequency analysis (770, InBody, Seoul, South Korea)";
 ELSE ~ NA)</t>
+  </si>
+  <si>
+    <t>case_when(
+fq241 == 1 | fq244 == 1 ~ 1L;
+fq241 == 2 &amp; fq244 == 2 ~ 0L;
+fq241 == 2 | fq244 == 2 ~ 2L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>case_when(
+fq289 == 1 | fq319 == 1 | fq364 == 1 ~ 1L;
+fq289 == 2 &amp; fq319 == 2 &amp; fq364 ==0 ~ 0L ; 
+ELSE ~ NA_integer_)</t>
   </si>
 </sst>
 </file>
@@ -3481,10 +3481,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3904,10 +3900,10 @@
         <v>17</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="V1" s="10" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="W1" s="10" t="s">
         <v>18</v>
@@ -4144,7 +4140,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>484</v>
@@ -4233,7 +4229,7 @@
         <v>493</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="60" x14ac:dyDescent="0.25">
@@ -4404,13 +4400,13 @@
         <v>493</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="Z10" s="1" t="s">
         <v>507</v>
       </c>
       <c r="AB10" s="12" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4475,10 +4471,10 @@
         <v>783</v>
       </c>
       <c r="AA11" s="15" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4543,7 +4539,7 @@
         <v>785</v>
       </c>
       <c r="AA12" s="15" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="AB12" s="12" t="s">
         <v>790</v>
@@ -4596,7 +4592,7 @@
         <v>512</v>
       </c>
       <c r="U13" s="12" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="V13" s="11" t="s">
         <v>514</v>
@@ -4673,7 +4669,7 @@
         <v>786</v>
       </c>
       <c r="AA14" s="15" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="AB14" s="12" t="s">
         <v>790</v>
@@ -4726,7 +4722,7 @@
         <v>512</v>
       </c>
       <c r="U15" s="12" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="V15" s="11" t="s">
         <v>514</v>
@@ -4788,7 +4784,7 @@
         <v>512</v>
       </c>
       <c r="U16" s="12" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="V16" s="11" t="s">
         <v>514</v>
@@ -4850,7 +4846,7 @@
         <v>512</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="V17" s="11" t="s">
         <v>514</v>
@@ -4912,7 +4908,7 @@
         <v>512</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="V18" s="11" t="s">
         <v>514</v>
@@ -4974,7 +4970,7 @@
         <v>512</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="V19" s="11" t="s">
         <v>474</v>
@@ -4989,7 +4985,7 @@
         <v>515</v>
       </c>
       <c r="AA19" s="15" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="AB19" s="12" t="s">
         <v>791</v>
@@ -5113,7 +5109,7 @@
         <v>560</v>
       </c>
       <c r="AB21" s="12" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -5172,7 +5168,7 @@
         <v>776</v>
       </c>
       <c r="AB22" s="12" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="180" x14ac:dyDescent="0.25">
@@ -5284,7 +5280,7 @@
         <v>527</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="Z24" s="2" t="s">
         <v>540</v>
@@ -5838,7 +5834,7 @@
         <v>359</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>474</v>
@@ -5850,7 +5846,7 @@
         <v>486</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="195" x14ac:dyDescent="0.25">
@@ -5873,7 +5869,7 @@
         <v>349</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>474</v>
@@ -5885,10 +5881,10 @@
         <v>527</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -5938,7 +5934,7 @@
         <v>360</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>474</v>
@@ -5950,13 +5946,13 @@
         <v>486</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>570</v>
       </c>
       <c r="AB36" s="12" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="37" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6006,7 +6002,7 @@
         <v>360</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>474</v>
@@ -6018,13 +6014,13 @@
         <v>486</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>570</v>
       </c>
       <c r="AB37" s="12" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="38" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6074,7 +6070,7 @@
         <v>578</v>
       </c>
       <c r="U38" s="12" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>474</v>
@@ -6086,13 +6082,13 @@
         <v>486</v>
       </c>
       <c r="Y38" s="12" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>570</v>
       </c>
       <c r="AB38" s="12" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -6136,7 +6132,7 @@
         <v>514</v>
       </c>
       <c r="AB39" s="12" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="40" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -6180,7 +6176,7 @@
         <v>584</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>474</v>
@@ -6192,14 +6188,14 @@
         <v>493</v>
       </c>
       <c r="Y40" s="12" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="Z40" s="2"/>
       <c r="AA40" s="15" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="AB40" s="12" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
@@ -6334,7 +6330,7 @@
         <v>776</v>
       </c>
       <c r="AB43" s="12" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6393,7 +6389,7 @@
         <v>776</v>
       </c>
       <c r="AB44" s="12" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6452,7 +6448,7 @@
         <v>776</v>
       </c>
       <c r="AB45" s="12" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6517,7 +6513,7 @@
         <v>602</v>
       </c>
       <c r="AB46" s="12" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6576,7 +6572,7 @@
         <v>776</v>
       </c>
       <c r="AB47" s="12" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6903,7 +6899,7 @@
         <v>760</v>
       </c>
       <c r="AB54" s="12" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -7072,7 +7068,7 @@
       </c>
       <c r="AA57" s="14"/>
       <c r="AB57" s="12" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -7134,7 +7130,7 @@
         <v>486</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="Z58" s="2" t="s">
         <v>772</v>
@@ -7349,13 +7345,13 @@
         <v>638</v>
       </c>
       <c r="Y62" s="15" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="Z62" s="2" t="s">
         <v>773</v>
       </c>
       <c r="AB62" s="12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -7535,7 +7531,7 @@
         <v>761</v>
       </c>
       <c r="AB65" s="12" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -7635,13 +7631,13 @@
         <v>638</v>
       </c>
       <c r="Y67" s="15" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="Z67" s="2" t="s">
         <v>650</v>
       </c>
       <c r="AB67" s="12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="255" x14ac:dyDescent="0.25">
@@ -7704,7 +7700,7 @@
       </c>
       <c r="AA68" s="1"/>
       <c r="AB68" s="12" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="69" spans="1:29" ht="255" x14ac:dyDescent="0.25">
@@ -7763,7 +7759,7 @@
         <v>514</v>
       </c>
       <c r="AB69" s="12" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7869,7 +7865,7 @@
         <v>663</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="V71" s="1" t="s">
         <v>474</v>
@@ -7887,7 +7883,7 @@
         <v>666</v>
       </c>
       <c r="AB71" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="72" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -7916,7 +7912,7 @@
         <v>446</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>667</v>
@@ -7947,19 +7943,19 @@
         <v>493</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="Z72" s="2" t="s">
         <v>774</v>
       </c>
       <c r="AA72" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="AB72" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="AC72" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="120" x14ac:dyDescent="0.25">
@@ -8009,7 +8005,7 @@
         <v>674</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="V73" s="1" t="s">
         <v>474</v>
@@ -8024,7 +8020,7 @@
         <v>820</v>
       </c>
       <c r="AB73" s="12" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="405" x14ac:dyDescent="0.25">
@@ -8053,7 +8049,7 @@
         <v>446</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>676</v>
@@ -8083,16 +8079,16 @@
         <v>527</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="Z74" s="2" t="s">
         <v>762</v>
       </c>
       <c r="AB74" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="AC74" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -8348,7 +8344,7 @@
         <v>822</v>
       </c>
       <c r="AB79" s="12" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="150" x14ac:dyDescent="0.25">
@@ -8737,7 +8733,7 @@
         <v>520</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="V86" s="1" t="s">
         <v>474</v>
@@ -8749,13 +8745,13 @@
         <v>527</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>826</v>
+        <v>895</v>
       </c>
       <c r="Z86" s="2" t="s">
         <v>710</v>
       </c>
       <c r="AB86" s="12" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="87" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8817,10 +8813,10 @@
         <v>527</v>
       </c>
       <c r="Y87" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="AB87" s="12" t="s">
         <v>824</v>
-      </c>
-      <c r="AB87" s="12" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="88" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9017,7 +9013,7 @@
         <v>466</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>763</v>
@@ -9044,13 +9040,13 @@
         <v>527</v>
       </c>
       <c r="Y91" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="Z91" s="2" t="s">
         <v>765</v>
       </c>
       <c r="AB91" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="92" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9106,13 +9102,13 @@
         <v>527</v>
       </c>
       <c r="Y92" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="Z92" s="2" t="s">
         <v>765</v>
       </c>
       <c r="AB92" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="93" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9168,13 +9164,13 @@
         <v>527</v>
       </c>
       <c r="Y93" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="Z93" s="2" t="s">
         <v>765</v>
       </c>
       <c r="AB93" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="94" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9221,7 +9217,7 @@
         <v>727</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="V94" s="1" t="s">
         <v>474</v>
@@ -9233,7 +9229,7 @@
         <v>527</v>
       </c>
       <c r="Y94" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="Z94" s="1" t="s">
         <v>766</v>
@@ -9418,13 +9414,13 @@
         <v>527</v>
       </c>
       <c r="Y98" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="Z98" s="2" t="s">
         <v>728</v>
       </c>
       <c r="AB98" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="99" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9471,7 +9467,7 @@
         <v>727</v>
       </c>
       <c r="U99" s="12" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="V99" s="1" t="s">
         <v>474</v>
@@ -9483,13 +9479,13 @@
         <v>527</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="Z99" s="2" t="s">
         <v>734</v>
       </c>
       <c r="AB99" s="12" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="100" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9545,13 +9541,13 @@
         <v>527</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="Z100" s="2" t="s">
         <v>728</v>
       </c>
       <c r="AB100" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="101" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9607,13 +9603,13 @@
         <v>527</v>
       </c>
       <c r="Y101" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="Z101" s="2" t="s">
         <v>728</v>
       </c>
       <c r="AB101" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="102" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9711,13 +9707,13 @@
         <v>527</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="Z103" s="2" t="s">
         <v>728</v>
       </c>
       <c r="AB103" s="12" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="104" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9949,7 +9945,7 @@
         <v>527</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="Z108" s="2"/>
     </row>
@@ -10006,7 +10002,7 @@
         <v>527</v>
       </c>
       <c r="Y109" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="Z109" s="2"/>
     </row>
@@ -10281,7 +10277,7 @@
         <v>520</v>
       </c>
       <c r="U114" s="12" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="V114" s="1" t="s">
         <v>474</v>
@@ -10299,7 +10295,7 @@
         <v>753</v>
       </c>
       <c r="AB114" s="12" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="115" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10346,7 +10342,7 @@
         <v>520</v>
       </c>
       <c r="U115" s="12" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="V115" s="1" t="s">
         <v>474</v>
@@ -10364,7 +10360,7 @@
         <v>753</v>
       </c>
       <c r="AB115" s="12" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="116" spans="1:28" ht="45" x14ac:dyDescent="0.25">

--- a/baseline/data_processing_elements-NES.xlsx
+++ b/baseline/data_processing_elements-NES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbtiali\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5098D060-15A2-4ADF-9F0C-4987B471B465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAEEB5E-2402-491F-9EEE-006B1A0C8ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="897">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="906">
   <si>
     <t>index</t>
   </si>
@@ -1622,10 +1622,6 @@
   </si>
   <si>
     <t>recode</t>
-  </si>
-  <si>
-    <t>bq1;
-bq2</t>
   </si>
   <si>
     <t>Date of baseline questionnaire;
@@ -2727,9 +2723,6 @@
 Added question for cohort to confirm input variable date and ask what the difference with physical exam date is.</t>
   </si>
   <si>
-    <t>lubridate::interval(as.Date(bq1), as.Date(bq2)) %/% lubridate::years(1)</t>
-  </si>
-  <si>
     <t>The algorithm should work, but I suggested a lubridate approach that's a little simpler and calculates years directly. The inputs are already texts in format YYYY-MM-DD.</t>
   </si>
   <si>
@@ -2805,25 +2798,12 @@
 Note on status_detail: If you did recode "." values, then it would be compatible, not identical.</t>
   </si>
   <si>
-    <t>case_when(
-!is.na(e3) ~ 2L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>round( e3/ ((e2/100)^2), 2)</t>
-  </si>
-  <si>
     <t>Height needs to be converted to meters. 
 There are no "." values.</t>
   </si>
   <si>
     <t>I would normally suggest writing the algorithm statements in the opposite order (coding "yes" first).
 Because there is a separate variable for retired = 1, I don't think we need to apply the condition in the DataSchema variable that they say No to employed? To verify.</t>
-  </si>
-  <si>
-    <t>case_when(
-!is.na(e4) ~ 2L;
-ELSE ~ NA_integer_)</t>
   </si>
   <si>
     <t>If a variable is used in the algorithm but not specified in input_variables, it should return an error when running harmo_process().</t>
@@ -3044,9 +3024,6 @@
     <t>Since there are no "." values, simplified algorithm. 
 Did we check that the algorithm as written works? I don't think you can usually use rowMeans as is within case_when.
 --&gt; Simplified to use 'operation'.</t>
-  </si>
-  <si>
-    <t>(e9 + e13 + e17 + e21) %&gt;% round(., 0)</t>
   </si>
   <si>
     <t>"Yes" responses to study variable "Are you fasted for 4 hours?" are considered as DataSchema category "long fast". "No" responses are considered as unknown.</t>
@@ -3307,14 +3284,6 @@
 questionnaire_date</t>
   </si>
   <si>
-    <t>ifelse(body_fat_mass_kg &gt; 0, body_fat_mass_kg/e3*100,NA)</t>
-  </si>
-  <si>
-    <t>case_when(year(questionnaire_date) == 2021 &amp; !is.na(body_fat_mass_kg) &amp; body_fat_mass_kg &gt; 0 ~ "Single-frequency analysis (1500, Bodystat, Douglas, Isle of Man)";
-year(questionnaire_date) &gt; 2021 &amp; !is.na(body_fat_mass_kg) &amp; body_fat_mass_kg &gt; 0~ "multi-frequency analysis (770, InBody, Seoul, South Korea)";
-ELSE ~ NA)</t>
-  </si>
-  <si>
     <t>case_when(
 fq241 == 1 | fq244 == 1 ~ 1L;
 fq241 == 2 &amp; fq244 == 2 ~ 0L;
@@ -3326,6 +3295,64 @@
 fq289 == 1 | fq319 == 1 | fq364 == 1 ~ 1L;
 fq289 == 2 &amp; fq319 == 2 &amp; fq364 ==0 ~ 0L ; 
 ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>questionnaire_date;
+bq2</t>
+  </si>
+  <si>
+    <t>lubridate::interval(as.Date(questionnaire_date), as.Date(bq2)) %/% lubridate::years(1)</t>
+  </si>
+  <si>
+    <t>as.numeric(e32)</t>
+  </si>
+  <si>
+    <t>as.numeric(fq12)</t>
+  </si>
+  <si>
+    <t>as.numeric(e2)</t>
+  </si>
+  <si>
+    <t>as.numeric(e3)</t>
+  </si>
+  <si>
+    <t>case_when(
+!is.na(as.numeric(e3)) ~ 2L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>round( as.numeric(e3)/ ((as.numeric(e2)/100)^2), 2)</t>
+  </si>
+  <si>
+    <t>as.numeric(e4)</t>
+  </si>
+  <si>
+    <t>case_when(
+!is.na(as.numeric(e4)) ~ 2L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>ifelse(as.numeric(body_fat_mass_kg) &gt; 0, as.numeric(body_fat_mass_kg)/as.numeric(e3)*100,NA)</t>
+  </si>
+  <si>
+    <t>case_when(lubridate::year(questionnaire_date) == 2021 &amp; !is.na(as.numeric(body_fat_mass_kg)) &amp; as.numeric(body_fat_mass_kg) &gt; 0 ~ "Single-frequency analysis (1500, Bodystat, Douglas, Isle of Man)";
+lubridate::year(questionnaire_date) &gt; 2021 &amp; !is.na(as.numeric(body_fat_mass_kg)) &amp; as.numeric(body_fat_mass_kg) &gt; 0~ "multi-frequency analysis (770, InBody, Seoul, South Korea)";
+ELSE ~ NA)</t>
+  </si>
+  <si>
+    <t>(as.numeric(e9) + as.numeric(e13) + as.numeric(e17) + as.numeric(e21)) %&gt;% round(., 0)</t>
+  </si>
+  <si>
+    <t>as.numeric(e29)</t>
+  </si>
+  <si>
+    <t>as.numeric(e30)</t>
+  </si>
+  <si>
+    <t>as.numeric(e31)</t>
+  </si>
+  <si>
+    <t>as.numeric(e36)</t>
   </si>
 </sst>
 </file>
@@ -3900,10 +3927,10 @@
         <v>17</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="V1" s="10" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="W1" s="10" t="s">
         <v>18</v>
@@ -3941,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>28</v>
@@ -3995,7 +4022,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>29</v>
@@ -4034,7 +4061,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>30</v>
@@ -4070,7 +4097,7 @@
         <v>480</v>
       </c>
       <c r="AB4" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -4078,7 +4105,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>31</v>
@@ -4117,7 +4144,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -4140,7 +4167,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>484</v>
@@ -4167,16 +4194,16 @@
         <v>475</v>
       </c>
       <c r="X6" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="AA6" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="Y6" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="AA6" s="15" t="s">
+      <c r="AB6" s="12" t="s">
         <v>777</v>
-      </c>
-      <c r="AB6" s="12" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="45" x14ac:dyDescent="0.25">
@@ -4184,7 +4211,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>33</v>
@@ -4229,7 +4256,7 @@
         <v>493</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="60" x14ac:dyDescent="0.25">
@@ -4237,7 +4264,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>34</v>
@@ -4258,40 +4285,40 @@
         <v>396</v>
       </c>
       <c r="L8" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="V8" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>486</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>779</v>
+        <v>890</v>
       </c>
       <c r="AB8" s="12" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="165" x14ac:dyDescent="0.25">
@@ -4299,7 +4326,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>35</v>
@@ -4320,37 +4347,37 @@
         <v>445</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="V9" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X9" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AA9" s="15" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AB9" s="12" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="135" x14ac:dyDescent="0.25">
@@ -4358,7 +4385,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>36</v>
@@ -4379,34 +4406,34 @@
         <v>446</v>
       </c>
       <c r="L10" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="V10" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X10" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AB10" s="12" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4414,7 +4441,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>37</v>
@@ -4438,43 +4465,43 @@
         <v>446</v>
       </c>
       <c r="L11" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U11" s="12" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="V11" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X11" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AA11" s="15" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="AB11" s="12" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4482,7 +4509,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>38</v>
@@ -4506,43 +4533,43 @@
         <v>446</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U12" s="12" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="V12" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X12" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AA12" s="15" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="AB12" s="12" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4550,7 +4577,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>39</v>
@@ -4574,37 +4601,37 @@
         <v>446</v>
       </c>
       <c r="L13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S13" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="V13" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="W13" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="U13" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="V13" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="X13" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4612,7 +4639,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>40</v>
@@ -4636,43 +4663,43 @@
         <v>446</v>
       </c>
       <c r="L14" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U14" s="12" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="V14" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X14" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AA14" s="15" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="AB14" s="12" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4680,7 +4707,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>41</v>
@@ -4704,37 +4731,37 @@
         <v>446</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S15" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="V15" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="W15" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="U15" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="V15" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="X15" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:32" ht="75" x14ac:dyDescent="0.25">
@@ -4742,7 +4769,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>42</v>
@@ -4766,37 +4793,37 @@
         <v>446</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S16" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="U16" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="V16" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="W16" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="U16" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="V16" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="X16" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -4804,7 +4831,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>43</v>
@@ -4828,37 +4855,37 @@
         <v>446</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S17" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="U17" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="V17" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="W17" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="U17" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="V17" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="X17" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -4866,7 +4893,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>44</v>
@@ -4890,37 +4917,37 @@
         <v>446</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S18" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="U18" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="W18" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="U18" s="12" t="s">
-        <v>846</v>
-      </c>
-      <c r="V18" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="X18" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -4928,7 +4955,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>45</v>
@@ -4952,43 +4979,43 @@
         <v>446</v>
       </c>
       <c r="L19" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="V19" s="11" t="s">
         <v>474</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X19" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AA19" s="15" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="AB19" s="12" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -4996,7 +5023,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>46</v>
@@ -5017,22 +5044,22 @@
         <v>447</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="O20" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="V20" s="1" t="s">
         <v>474</v>
@@ -5044,7 +5071,7 @@
         <v>493</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5052,7 +5079,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>47</v>
@@ -5073,16 +5100,16 @@
         <v>448</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="M21" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>472</v>
@@ -5091,25 +5118,25 @@
         <v>482</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="V21" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="Z21" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AB21" s="12" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -5117,7 +5144,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>48</v>
@@ -5135,16 +5162,16 @@
         <v>355</v>
       </c>
       <c r="L22" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="M22" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>472</v>
@@ -5153,7 +5180,7 @@
         <v>482</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="V22" s="1" t="s">
         <v>474</v>
@@ -5162,13 +5189,13 @@
         <v>475</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>776</v>
+        <v>486</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>776</v>
+        <v>892</v>
       </c>
       <c r="AB22" s="12" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="180" x14ac:dyDescent="0.25">
@@ -5176,7 +5203,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>49</v>
@@ -5191,40 +5218,40 @@
         <v>349</v>
       </c>
       <c r="L23" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="V23" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W23" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X23" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AB23" s="12" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5232,7 +5259,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -5253,40 +5280,40 @@
         <v>449</v>
       </c>
       <c r="L24" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="M24" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="S24" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AB24" s="12" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5294,7 +5321,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>51</v>
@@ -5312,34 +5339,34 @@
         <v>450</v>
       </c>
       <c r="L25" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="O25" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="V25" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X25" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -5347,7 +5374,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>52</v>
@@ -5371,16 +5398,16 @@
         <v>477</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5388,7 +5415,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>53</v>
@@ -5409,16 +5436,16 @@
         <v>411</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>174</v>
       </c>
       <c r="N27" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="O27" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>472</v>
@@ -5436,13 +5463,13 @@
         <v>475</v>
       </c>
       <c r="X27" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
       </c>
       <c r="Y27" s="12" t="s">
-        <v>776</v>
+        <v>893</v>
       </c>
       <c r="AB27" s="12" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -5450,7 +5477,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>54</v>
@@ -5468,16 +5495,16 @@
         <v>452</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>174</v>
       </c>
       <c r="N28" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>472</v>
@@ -5492,16 +5519,16 @@
         <v>474</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X28" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y28" s="12" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="AB28" s="12" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -5509,7 +5536,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>55</v>
@@ -5530,16 +5557,16 @@
         <v>411</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>176</v>
       </c>
       <c r="N29" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>472</v>
@@ -5557,13 +5584,13 @@
         <v>475</v>
       </c>
       <c r="X29" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>776</v>
+        <v>894</v>
       </c>
       <c r="AB29" s="12" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -5571,7 +5598,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>56</v>
@@ -5589,16 +5616,16 @@
         <v>452</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>176</v>
       </c>
       <c r="N30" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="O30" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>472</v>
@@ -5613,16 +5640,16 @@
         <v>474</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X30" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y30" s="12" t="s">
-        <v>798</v>
+        <v>895</v>
       </c>
       <c r="AB30" s="12" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="165" x14ac:dyDescent="0.25">
@@ -5630,7 +5657,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>57</v>
@@ -5651,40 +5678,40 @@
         <v>411</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="R31" s="2" t="s">
+      <c r="S31" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="T31" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="T31" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="V31" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X31" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y31" s="12" t="s">
-        <v>799</v>
+        <v>896</v>
       </c>
       <c r="AB31" s="12" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5692,7 +5719,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>58</v>
@@ -5713,16 +5740,16 @@
         <v>411</v>
       </c>
       <c r="L32" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="M32" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>472</v>
@@ -5740,13 +5767,13 @@
         <v>475</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
       </c>
       <c r="Y32" s="12" t="s">
-        <v>776</v>
+        <v>897</v>
       </c>
       <c r="AB32" s="12" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="33" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -5754,7 +5781,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>59</v>
@@ -5772,16 +5799,16 @@
         <v>452</v>
       </c>
       <c r="L33" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="M33" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="O33" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="R33" s="1" t="s">
         <v>472</v>
@@ -5796,19 +5823,19 @@
         <v>474</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X33" s="11" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y33" s="12" t="s">
-        <v>802</v>
+        <v>898</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AB33" s="12" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
     </row>
     <row r="34" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -5816,7 +5843,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>60</v>
@@ -5834,19 +5861,19 @@
         <v>359</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="V34" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X34" s="1" t="s">
         <v>486</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="195" x14ac:dyDescent="0.25">
@@ -5854,7 +5881,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>61</v>
@@ -5869,22 +5896,22 @@
         <v>349</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
     </row>
     <row r="36" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -5892,7 +5919,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>62</v>
@@ -5913,16 +5940,16 @@
         <v>412</v>
       </c>
       <c r="L36" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="M36" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="O36" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="R36" s="1" t="s">
         <v>472</v>
@@ -5934,25 +5961,25 @@
         <v>360</v>
       </c>
       <c r="U36" s="12" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X36" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AB36" s="12" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="37" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -5960,7 +5987,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>63</v>
@@ -5981,16 +6008,16 @@
         <v>412</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="O37" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>472</v>
@@ -6002,25 +6029,25 @@
         <v>360</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X37" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AB37" s="12" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="38" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6028,7 +6055,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>64</v>
@@ -6049,16 +6076,16 @@
         <v>412</v>
       </c>
       <c r="L38" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="N38" s="1" t="s">
+      <c r="O38" s="2" t="s">
         <v>576</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>577</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>472</v>
@@ -6067,28 +6094,28 @@
         <v>482</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="U38" s="12" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X38" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y38" s="12" t="s">
-        <v>852</v>
+        <v>901</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AB38" s="12" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="39" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -6096,7 +6123,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>65</v>
@@ -6120,19 +6147,19 @@
         <v>477</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AB39" s="12" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="40" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -6140,7 +6167,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>66</v>
@@ -6158,44 +6185,44 @@
         <v>453</v>
       </c>
       <c r="L40" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="O40" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X40" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y40" s="12" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="Z40" s="2"/>
       <c r="AA40" s="15" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="AB40" s="12" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.25">
@@ -6203,7 +6230,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>67</v>
@@ -6224,16 +6251,16 @@
         <v>477</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
@@ -6241,7 +6268,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>68</v>
@@ -6262,16 +6289,16 @@
         <v>477</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6279,7 +6306,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>69</v>
@@ -6297,16 +6324,16 @@
         <v>365</v>
       </c>
       <c r="L43" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="M43" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="O43" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>472</v>
@@ -6315,7 +6342,7 @@
         <v>482</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>474</v>
@@ -6324,13 +6351,13 @@
         <v>475</v>
       </c>
       <c r="X43" s="11" t="s">
-        <v>776</v>
-      </c>
-      <c r="Y43" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>902</v>
       </c>
       <c r="AB43" s="12" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6338,7 +6365,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>70</v>
@@ -6356,16 +6383,16 @@
         <v>365</v>
       </c>
       <c r="L44" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="M44" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="O44" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>472</v>
@@ -6374,7 +6401,7 @@
         <v>482</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="V44" s="1" t="s">
         <v>474</v>
@@ -6383,13 +6410,13 @@
         <v>475</v>
       </c>
       <c r="X44" s="11" t="s">
-        <v>776</v>
-      </c>
-      <c r="Y44" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>903</v>
       </c>
       <c r="AB44" s="12" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="45" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6397,7 +6424,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>71</v>
@@ -6415,16 +6442,16 @@
         <v>365</v>
       </c>
       <c r="L45" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="M45" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="N45" s="1" t="s">
+      <c r="O45" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>472</v>
@@ -6433,7 +6460,7 @@
         <v>482</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="V45" s="1" t="s">
         <v>474</v>
@@ -6442,13 +6469,13 @@
         <v>475</v>
       </c>
       <c r="X45" s="11" t="s">
-        <v>776</v>
-      </c>
-      <c r="Y45" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>904</v>
       </c>
       <c r="AB45" s="12" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="120" x14ac:dyDescent="0.25">
@@ -6456,7 +6483,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>72</v>
@@ -6477,16 +6504,16 @@
         <v>414</v>
       </c>
       <c r="L46" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="M46" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>601</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>472</v>
@@ -6495,25 +6522,25 @@
         <v>482</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="V46" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AB46" s="12" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6521,7 +6548,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>73</v>
@@ -6539,16 +6566,16 @@
         <v>365</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="M47" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="N47" s="1" t="s">
+      <c r="O47" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="O47" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>472</v>
@@ -6557,7 +6584,7 @@
         <v>482</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="V47" s="1" t="s">
         <v>474</v>
@@ -6566,13 +6593,13 @@
         <v>475</v>
       </c>
       <c r="X47" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
       </c>
       <c r="Y47" s="11" t="s">
-        <v>776</v>
+        <v>891</v>
       </c>
       <c r="AB47" s="12" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6580,7 +6607,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>74</v>
@@ -6598,19 +6625,19 @@
         <v>366</v>
       </c>
       <c r="L48" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="M48" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="N48" s="1" t="s">
+      <c r="O48" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="O48" s="2" t="s">
+      <c r="P48" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>611</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>472</v>
@@ -6619,7 +6646,7 @@
         <v>482</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="V48" s="1" t="s">
         <v>474</v>
@@ -6628,10 +6655,10 @@
         <v>475</v>
       </c>
       <c r="X48" s="11" t="s">
-        <v>776</v>
+        <v>486</v>
       </c>
       <c r="Y48" s="11" t="s">
-        <v>776</v>
+        <v>905</v>
       </c>
     </row>
     <row r="49" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6639,7 +6666,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>75</v>
@@ -6663,16 +6690,16 @@
         <v>477</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="50" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6680,7 +6707,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>76</v>
@@ -6701,16 +6728,16 @@
         <v>477</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="51" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -6718,7 +6745,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>77</v>
@@ -6742,16 +6769,16 @@
         <v>477</v>
       </c>
       <c r="V51" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X51" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="52" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -6759,7 +6786,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>78</v>
@@ -6783,16 +6810,16 @@
         <v>477</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X52" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y52" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="53" spans="1:28" x14ac:dyDescent="0.25">
@@ -6800,7 +6827,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>79</v>
@@ -6821,16 +6848,16 @@
         <v>477</v>
       </c>
       <c r="V53" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X53" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y53" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="54" spans="1:28" ht="225" x14ac:dyDescent="0.25">
@@ -6838,7 +6865,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>80</v>
@@ -6859,47 +6886,47 @@
         <v>418</v>
       </c>
       <c r="L54" s="12" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="N54" s="12" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="O54" s="12" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>472</v>
       </c>
       <c r="S54" s="2"/>
       <c r="T54" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="V54" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X54" s="11" t="s">
         <v>486</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="Z54" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AB54" s="12" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
     </row>
     <row r="55" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -6907,7 +6934,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>81</v>
@@ -6928,16 +6955,16 @@
         <v>477</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="75" x14ac:dyDescent="0.25">
@@ -6945,7 +6972,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>82</v>
@@ -6966,22 +6993,22 @@
         <v>456</v>
       </c>
       <c r="L56" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="M56" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="O56" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="R56" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="V56" s="1" t="s">
         <v>474</v>
@@ -6993,16 +7020,16 @@
         <v>493</v>
       </c>
       <c r="Y56" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="Z56" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="Z56" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="AA56" s="12" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="AB56" s="12" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
     </row>
     <row r="57" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -7010,7 +7037,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>83</v>
@@ -7028,19 +7055,19 @@
         <v>457</v>
       </c>
       <c r="L57" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="N57" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="O57" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="N57" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>770</v>
-      </c>
       <c r="P57" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>472</v>
@@ -7049,26 +7076,26 @@
         <v>482</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="V57" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W57" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="X57" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y57" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z57" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AA57" s="14"/>
       <c r="AB57" s="12" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="90" x14ac:dyDescent="0.25">
@@ -7076,7 +7103,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>84</v>
@@ -7097,19 +7124,19 @@
         <v>420</v>
       </c>
       <c r="L58" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="M58" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="N58" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="O58" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="N58" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="O58" s="2" t="s">
-        <v>770</v>
-      </c>
       <c r="P58" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>472</v>
@@ -7118,25 +7145,25 @@
         <v>482</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="V58" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X58" s="1" t="s">
         <v>486</v>
       </c>
       <c r="Y58" s="2" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="Z58" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AB58" s="12" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -7144,7 +7171,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>85</v>
@@ -7162,34 +7189,34 @@
         <v>355</v>
       </c>
       <c r="L59" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="M59" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="N59" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="N59" s="1" t="s">
+      <c r="O59" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="V59" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="X59" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y59" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="60" spans="1:28" ht="165" x14ac:dyDescent="0.25">
@@ -7197,7 +7224,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>86</v>
@@ -7218,37 +7245,37 @@
         <v>458</v>
       </c>
       <c r="L60" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="M60" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="N60" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="N60" s="1" t="s">
+      <c r="O60" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="R60" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="V60" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X60" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y60" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="AB60" s="12" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="61" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -7256,7 +7283,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>87</v>
@@ -7277,16 +7304,16 @@
         <v>477</v>
       </c>
       <c r="V61" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y61" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
@@ -7294,7 +7321,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>88</v>
@@ -7315,43 +7342,43 @@
         <v>460</v>
       </c>
       <c r="L62" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="M62" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="M62" s="2" t="s">
-        <v>640</v>
-      </c>
       <c r="N62" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="O62" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="O62" s="2" t="s">
+      <c r="Q62" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V62" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X62" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="Y62" s="15" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="Z62" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AB62" s="12" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
     </row>
     <row r="63" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -7359,7 +7386,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>89</v>
@@ -7377,40 +7404,40 @@
         <v>460</v>
       </c>
       <c r="L63" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="M63" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="N63" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="N63" s="1" t="s">
+      <c r="O63" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="O63" s="2" t="s">
+      <c r="Q63" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="R63" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V63" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X63" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y63" s="2" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="AB63" s="12" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="64" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -7418,7 +7445,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>90</v>
@@ -7436,40 +7463,40 @@
         <v>460</v>
       </c>
       <c r="L64" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="M64" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="M64" s="2" t="s">
+      <c r="N64" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="O64" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="N64" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>637</v>
-      </c>
       <c r="Q64" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V64" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X64" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="AB64" s="12" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="65" spans="1:29" ht="180" x14ac:dyDescent="0.25">
@@ -7477,7 +7504,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>91</v>
@@ -7495,43 +7522,43 @@
         <v>461</v>
       </c>
       <c r="L65" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="M65" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="N65" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="N65" s="1" t="s">
+      <c r="O65" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>644</v>
-      </c>
       <c r="Q65" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R65" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V65" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X65" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y65" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="Z65" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AB65" s="12" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
     </row>
     <row r="66" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -7539,7 +7566,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>92</v>
@@ -7563,16 +7590,16 @@
         <v>477</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y66" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
@@ -7580,7 +7607,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>93</v>
@@ -7601,43 +7628,43 @@
         <v>460</v>
       </c>
       <c r="L67" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="M67" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="M67" s="2" t="s">
+      <c r="N67" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="N67" s="1" t="s">
+      <c r="O67" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="O67" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="Q67" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V67" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X67" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="Y67" s="15" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="Z67" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AB67" s="12" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
     </row>
     <row r="68" spans="1:29" ht="255" x14ac:dyDescent="0.25">
@@ -7645,7 +7672,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>94</v>
@@ -7666,41 +7693,41 @@
         <v>422</v>
       </c>
       <c r="L68" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="M68" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="M68" s="2" t="s">
+      <c r="N68" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="O68" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="Q68" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V68" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W68" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="X68" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y68" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AA68" s="1"/>
       <c r="AB68" s="12" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
     </row>
     <row r="69" spans="1:29" ht="255" x14ac:dyDescent="0.25">
@@ -7708,7 +7735,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>95</v>
@@ -7726,40 +7753,40 @@
         <v>462</v>
       </c>
       <c r="L69" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="M69" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="M69" s="2" t="s">
+      <c r="N69" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="O69" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="N69" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="O69" s="2" t="s">
-        <v>653</v>
-      </c>
       <c r="Q69" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="V69" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W69" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="X69" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y69" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AB69" s="12" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
     </row>
     <row r="70" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -7767,7 +7794,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>96</v>
@@ -7785,22 +7812,22 @@
         <v>463</v>
       </c>
       <c r="L70" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="M70" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="N70" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="N70" s="1" t="s">
+      <c r="O70" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="O70" s="2" t="s">
+      <c r="P70" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="P70" s="1" t="s">
+      <c r="Q70" s="1" t="s">
         <v>658</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>659</v>
       </c>
       <c r="R70" s="1" t="s">
         <v>472</v>
@@ -7809,22 +7836,22 @@
         <v>482</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="V70" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W70" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="X70" s="11" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y70" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AB70" s="12" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
     <row r="71" spans="1:29" ht="105" x14ac:dyDescent="0.25">
@@ -7832,7 +7859,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>97</v>
@@ -7850,40 +7877,40 @@
         <v>464</v>
       </c>
       <c r="L71" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="M71" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="M71" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="O71" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="V71" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X71" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y71" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="Z71" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="Z71" s="2" t="s">
-        <v>666</v>
-      </c>
       <c r="AB71" s="1" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
     </row>
     <row r="72" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -7891,7 +7918,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>98</v>
@@ -7912,50 +7939,50 @@
         <v>446</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="M72" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="O72" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="N72" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>668</v>
-      </c>
       <c r="Q72" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R72" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="U72" s="1"/>
       <c r="V72" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X72" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y72" s="2" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="Z72" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AA72" s="2" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="AB72" s="2" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="AC72" s="1" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
     </row>
     <row r="73" spans="1:29" ht="120" x14ac:dyDescent="0.25">
@@ -7963,7 +7990,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>99</v>
@@ -7984,43 +8011,43 @@
         <v>446</v>
       </c>
       <c r="L73" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="M73" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="M73" s="2" t="s">
+      <c r="N73" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="N73" s="1" t="s">
+      <c r="O73" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="O73" s="2" t="s">
-        <v>673</v>
-      </c>
       <c r="Q73" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="V73" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X73" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y73" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="AB73" s="12" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="74" spans="1:29" ht="405" x14ac:dyDescent="0.25">
@@ -8028,7 +8055,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>100</v>
@@ -8049,46 +8076,46 @@
         <v>446</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="M74" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="O74" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="N74" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>677</v>
-      </c>
       <c r="Q74" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R74" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="V74" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X74" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y74" s="2" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="Z74" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AB74" s="2" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="AC74" s="1" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
     </row>
     <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -8096,7 +8123,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>101</v>
@@ -8117,16 +8144,16 @@
         <v>477</v>
       </c>
       <c r="V75" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X75" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y75" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -8134,7 +8161,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>102</v>
@@ -8155,16 +8182,16 @@
         <v>477</v>
       </c>
       <c r="V76" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X76" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y76" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="77" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -8172,7 +8199,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>103</v>
@@ -8190,34 +8217,34 @@
         <v>465</v>
       </c>
       <c r="L77" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="M77" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="M77" s="2" t="s">
+      <c r="N77" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="O77" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="R77" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="V77" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X77" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y77" s="2" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
     </row>
     <row r="78" spans="1:29" ht="210" x14ac:dyDescent="0.25">
@@ -8225,7 +8252,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>104</v>
@@ -8246,40 +8273,40 @@
         <v>466</v>
       </c>
       <c r="L78" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="N78" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="N78" s="1" t="s">
+      <c r="O78" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="O78" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U78" s="12" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="V78" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X78" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y78" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Z78" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="79" spans="1:29" ht="150" x14ac:dyDescent="0.25">
@@ -8287,7 +8314,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>105</v>
@@ -8311,40 +8338,40 @@
         <v>466</v>
       </c>
       <c r="L79" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="M79" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="N79" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O79" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="N79" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S79" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="V79" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W79" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X79" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y79" s="2" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="AB79" s="12" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
     </row>
     <row r="80" spans="1:29" ht="150" x14ac:dyDescent="0.25">
@@ -8352,7 +8379,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>106</v>
@@ -8376,22 +8403,22 @@
         <v>466</v>
       </c>
       <c r="L80" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="M80" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="M80" s="2" t="s">
+      <c r="N80" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O80" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S80" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V80" s="1" t="s">
         <v>474</v>
@@ -8403,7 +8430,7 @@
         <v>493</v>
       </c>
       <c r="Y80" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="81" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8411,7 +8438,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>107</v>
@@ -8438,16 +8465,16 @@
         <v>477</v>
       </c>
       <c r="V81" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X81" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y81" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="82" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8455,7 +8482,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>108</v>
@@ -8479,22 +8506,22 @@
         <v>466</v>
       </c>
       <c r="L82" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="M82" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="M82" s="2" t="s">
+      <c r="N82" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O82" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S82" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V82" s="1" t="s">
         <v>474</v>
@@ -8506,7 +8533,7 @@
         <v>493</v>
       </c>
       <c r="Y82" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="83" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8514,7 +8541,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>109</v>
@@ -8538,22 +8565,22 @@
         <v>466</v>
       </c>
       <c r="L83" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="M83" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="M83" s="2" t="s">
+      <c r="N83" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O83" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="R83" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V83" s="1" t="s">
         <v>474</v>
@@ -8565,7 +8592,7 @@
         <v>493</v>
       </c>
       <c r="Y83" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="84" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8573,7 +8600,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>110</v>
@@ -8597,22 +8624,22 @@
         <v>466</v>
       </c>
       <c r="L84" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="M84" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="M84" s="2" t="s">
+      <c r="N84" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O84" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O84" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S84" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V84" s="1" t="s">
         <v>474</v>
@@ -8624,7 +8651,7 @@
         <v>493</v>
       </c>
       <c r="Y84" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="85" spans="1:28" ht="195" x14ac:dyDescent="0.25">
@@ -8632,7 +8659,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>111</v>
@@ -8656,22 +8683,22 @@
         <v>466</v>
       </c>
       <c r="L85" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="M85" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="M85" s="2" t="s">
+      <c r="N85" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O85" s="2" t="s">
         <v>704</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O85" s="2" t="s">
-        <v>705</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S85" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V85" s="1" t="s">
         <v>474</v>
@@ -8683,7 +8710,7 @@
         <v>493</v>
       </c>
       <c r="Y85" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="86" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8691,7 +8718,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>112</v>
@@ -8715,43 +8742,43 @@
         <v>466</v>
       </c>
       <c r="L86" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="M86" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="N86" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="N86" s="2" t="s">
+      <c r="O86" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="O86" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U86" s="12" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="V86" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X86" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y86" s="2" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="Z86" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AB86" s="12" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
     </row>
     <row r="87" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8759,7 +8786,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>113</v>
@@ -8783,40 +8810,40 @@
         <v>466</v>
       </c>
       <c r="L87" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="M87" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="M87" s="2" t="s">
+      <c r="N87" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O87" s="2" t="s">
         <v>712</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="R87" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S87" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U87" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="V87" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X87" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="AB87" s="12" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
     </row>
     <row r="88" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -8824,7 +8851,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>114</v>
@@ -8848,22 +8875,22 @@
         <v>466</v>
       </c>
       <c r="L88" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="M88" s="2" t="s">
+      <c r="N88" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O88" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>717</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S88" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V88" s="1" t="s">
         <v>474</v>
@@ -8875,7 +8902,7 @@
         <v>493</v>
       </c>
       <c r="Y88" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="60" x14ac:dyDescent="0.25">
@@ -8883,7 +8910,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>115</v>
@@ -8901,34 +8928,34 @@
         <v>467</v>
       </c>
       <c r="L89" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="M89" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="M89" s="2" t="s">
+      <c r="O89" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="O89" s="2" t="s">
-        <v>720</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S89" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="V89" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X89" s="1" t="s">
         <v>493</v>
       </c>
       <c r="Y89" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="90" spans="1:28" ht="105" x14ac:dyDescent="0.25">
@@ -8936,7 +8963,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>116</v>
@@ -8957,22 +8984,22 @@
         <v>466</v>
       </c>
       <c r="L90" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="M90" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="M90" s="2" t="s">
+      <c r="N90" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O90" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O90" s="2" t="s">
-        <v>726</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S90" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V90" s="1" t="s">
         <v>474</v>
@@ -8984,7 +9011,7 @@
         <v>493</v>
       </c>
       <c r="Y90" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="91" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -8992,7 +9019,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>117</v>
@@ -9013,40 +9040,40 @@
         <v>466</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="M91" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N91" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R91" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V91" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X91" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y91" s="2" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="Z91" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AB91" s="12" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="92" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9054,7 +9081,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>118</v>
@@ -9075,40 +9102,40 @@
         <v>466</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M92" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O92" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N92" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R92" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V92" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X92" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y92" s="2" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="Z92" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AB92" s="12" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="93" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9116,7 +9143,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>119</v>
@@ -9137,40 +9164,40 @@
         <v>466</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="M93" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O93" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O93" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S93" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V93" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X93" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y93" s="2" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="Z93" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AB93" s="12" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="94" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9178,7 +9205,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>120</v>
@@ -9199,40 +9226,40 @@
         <v>466</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="M94" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O94" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R94" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="V94" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X94" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y94" s="2" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="Z94" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="95" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9240,7 +9267,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>121</v>
@@ -9264,16 +9291,16 @@
         <v>477</v>
       </c>
       <c r="V95" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z95" s="2"/>
     </row>
@@ -9282,7 +9309,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>122</v>
@@ -9306,16 +9333,16 @@
         <v>477</v>
       </c>
       <c r="V96" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X96" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z96" s="2"/>
     </row>
@@ -9324,7 +9351,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>123</v>
@@ -9348,16 +9375,16 @@
         <v>477</v>
       </c>
       <c r="V97" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z97" s="2"/>
     </row>
@@ -9366,7 +9393,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>124</v>
@@ -9387,40 +9414,40 @@
         <v>466</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M98" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O98" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S98" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V98" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y98" s="2" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="Z98" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AB98" s="12" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="99" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9428,7 +9455,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>125</v>
@@ -9449,43 +9476,43 @@
         <v>466</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="M99" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O99" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O99" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S99" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U99" s="12" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="V99" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W99" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y99" s="2" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="Z99" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AB99" s="12" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
     </row>
     <row r="100" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9493,7 +9520,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>126</v>
@@ -9514,40 +9541,40 @@
         <v>466</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M100" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O100" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O100" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S100" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V100" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W100" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X100" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y100" s="2" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="Z100" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AB100" s="12" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="101" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9555,7 +9582,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>127</v>
@@ -9576,40 +9603,40 @@
         <v>466</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M101" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O101" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O101" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V101" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W101" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y101" s="2" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="Z101" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AB101" s="12" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="102" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9617,7 +9644,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>128</v>
@@ -9641,16 +9668,16 @@
         <v>477</v>
       </c>
       <c r="V102" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W102" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y102" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z102" s="2"/>
     </row>
@@ -9659,7 +9686,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>129</v>
@@ -9680,40 +9707,40 @@
         <v>466</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="M103" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N103" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O103" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N103" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O103" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V103" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W103" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X103" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="Z103" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AB103" s="12" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="104" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9721,7 +9748,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>130</v>
@@ -9745,19 +9772,19 @@
         <v>477</v>
       </c>
       <c r="V104" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X104" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z104" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="105" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9765,7 +9792,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>131</v>
@@ -9789,19 +9816,19 @@
         <v>477</v>
       </c>
       <c r="V105" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X105" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y105" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z105" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="106" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9809,7 +9836,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>132</v>
@@ -9833,19 +9860,19 @@
         <v>477</v>
       </c>
       <c r="V106" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W106" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X106" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y106" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z106" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="107" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -9853,7 +9880,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>133</v>
@@ -9877,19 +9904,19 @@
         <v>477</v>
       </c>
       <c r="V107" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W107" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X107" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y107" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Z107" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="108" spans="1:28" ht="285" x14ac:dyDescent="0.25">
@@ -9897,7 +9924,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>134</v>
@@ -9918,34 +9945,34 @@
         <v>466</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="M108" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O108" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N108" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O108" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R108" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V108" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W108" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X108" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y108" s="2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="Z108" s="2"/>
     </row>
@@ -9954,7 +9981,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>135</v>
@@ -9975,34 +10002,34 @@
         <v>466</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="M109" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O109" s="2" t="s">
         <v>763</v>
-      </c>
-      <c r="N109" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O109" s="2" t="s">
-        <v>764</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="V109" s="1" t="s">
         <v>474</v>
       </c>
       <c r="W109" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="X109" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y109" s="2" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="Z109" s="2"/>
     </row>
@@ -10011,7 +10038,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>136</v>
@@ -10032,22 +10059,22 @@
         <v>466</v>
       </c>
       <c r="L110" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="M110" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="M110" s="2" t="s">
+      <c r="N110" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O110" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="N110" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O110" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="R110" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S110" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V110" s="1" t="s">
         <v>474</v>
@@ -10059,7 +10086,7 @@
         <v>493</v>
       </c>
       <c r="Y110" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="111" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10067,7 +10094,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>137</v>
@@ -10088,22 +10115,22 @@
         <v>466</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M111" s="2" t="s">
         <v>258</v>
       </c>
       <c r="N111" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S111" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V111" s="1" t="s">
         <v>474</v>
@@ -10115,7 +10142,7 @@
         <v>493</v>
       </c>
       <c r="Y111" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="112" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10123,7 +10150,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>138</v>
@@ -10144,22 +10171,22 @@
         <v>466</v>
       </c>
       <c r="L112" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="M112" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="M112" s="2" t="s">
+      <c r="N112" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="O112" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="N112" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="O112" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S112" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V112" s="1" t="s">
         <v>474</v>
@@ -10171,7 +10198,7 @@
         <v>493</v>
       </c>
       <c r="Y112" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="113" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10179,7 +10206,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>139</v>
@@ -10200,22 +10227,22 @@
         <v>466</v>
       </c>
       <c r="L113" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="M113" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="M113" s="2" t="s">
+      <c r="N113" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="N113" s="1" t="s">
+      <c r="O113" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="O113" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="R113" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S113" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="V113" s="1" t="s">
         <v>474</v>
@@ -10227,10 +10254,10 @@
         <v>493</v>
       </c>
       <c r="Y113" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Z113" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="114" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10238,7 +10265,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>140</v>
@@ -10259,25 +10286,25 @@
         <v>466</v>
       </c>
       <c r="L114" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="M114" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="M114" s="2" t="s">
+      <c r="N114" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="O114" s="2" t="s">
         <v>755</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="O114" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U114" s="12" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="V114" s="1" t="s">
         <v>474</v>
@@ -10289,13 +10316,13 @@
         <v>493</v>
       </c>
       <c r="Y114" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Z114" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AB114" s="12" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="115" spans="1:28" ht="150" x14ac:dyDescent="0.25">
@@ -10303,7 +10330,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>141</v>
@@ -10324,25 +10351,25 @@
         <v>466</v>
       </c>
       <c r="L115" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="M115" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="M115" s="2" t="s">
+      <c r="N115" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="O115" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="N115" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="O115" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>491</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="U115" s="12" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="V115" s="1" t="s">
         <v>474</v>
@@ -10354,13 +10381,13 @@
         <v>493</v>
       </c>
       <c r="Y115" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Z115" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AB115" s="12" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
     </row>
     <row r="116" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -10368,7 +10395,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>142</v>
@@ -10389,16 +10416,16 @@
         <v>477</v>
       </c>
       <c r="V116" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W116" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X116" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y116" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="117" spans="1:28" ht="45" x14ac:dyDescent="0.25">
@@ -10406,7 +10433,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>143</v>
@@ -10427,16 +10454,16 @@
         <v>477</v>
       </c>
       <c r="V117" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W117" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X117" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y117" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="118" spans="1:28" x14ac:dyDescent="0.25">
@@ -10444,7 +10471,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>144</v>
@@ -10465,16 +10492,16 @@
         <v>477</v>
       </c>
       <c r="V118" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W118" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X118" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y118" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="119" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10482,7 +10509,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>145</v>
@@ -10503,16 +10530,16 @@
         <v>477</v>
       </c>
       <c r="V119" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W119" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X119" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y119" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="120" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10520,7 +10547,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>146</v>
@@ -10541,16 +10568,16 @@
         <v>477</v>
       </c>
       <c r="V120" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W120" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X120" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y120" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="121" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10558,7 +10585,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>147</v>
@@ -10579,16 +10606,16 @@
         <v>477</v>
       </c>
       <c r="V121" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W121" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X121" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y121" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="1:28" ht="30" x14ac:dyDescent="0.25">
@@ -10596,7 +10623,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>148</v>
@@ -10617,16 +10644,16 @@
         <v>477</v>
       </c>
       <c r="V122" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="W122" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="X122" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Y122" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-NES.xlsx
+++ b/baseline/data_processing_elements-NES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sbtiali\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maelstrom\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAEEB5E-2402-491F-9EEE-006B1A0C8ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EC0DDE-2EDE-4B67-858B-6C9F0B0A8E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
   </bookViews>
   <sheets>
     <sheet name="DPE" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2055" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="908">
   <si>
     <t>index</t>
   </si>
@@ -3352,7 +3352,16 @@
     <t>as.numeric(e31)</t>
   </si>
   <si>
-    <t>as.numeric(e36)</t>
+    <t>The threshold of the machine used for analysis was 4 which is too high to get a proper distribution.</t>
+  </si>
+  <si>
+    <t>cancer_kidney</t>
+  </si>
+  <si>
+    <t>case_when(
+fq113 == 2 ~ 0L;
+cancer_kidney == 1 ~ 1L;
+ELSE ~ NA_integer_ )</t>
   </si>
 </sst>
 </file>
@@ -3828,44 +3837,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32FF9666-3C68-4610-B7F3-25EE531D7B07}">
   <dimension ref="A1:AF122"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="29" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40.7265625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.54296875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="70.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="28.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="32.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="70.7265625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="28.1796875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="32.453125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="42" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="53.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="3.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="4.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.81640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="53.7265625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="3.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.54296875" style="1" customWidth="1"/>
     <col min="18" max="18" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="45.85546875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.28515625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="32.140625" style="12" customWidth="1"/>
+    <col min="19" max="19" width="45.81640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.26953125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="32.1796875" style="12" customWidth="1"/>
     <col min="22" max="22" width="15" style="1" customWidth="1"/>
-    <col min="23" max="23" width="15.42578125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="16.140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="49.7109375" style="2" customWidth="1"/>
-    <col min="26" max="26" width="42.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="46.42578125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="54.140625" style="14" customWidth="1"/>
-    <col min="29" max="29" width="39.140625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.453125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="16.1796875" style="1" customWidth="1"/>
+    <col min="25" max="25" width="49.7265625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="42.26953125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="46.453125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="54.1796875" style="14" customWidth="1"/>
+    <col min="29" max="29" width="39.1796875" style="1" customWidth="1"/>
     <col min="30" max="30" width="29" style="1" customWidth="1"/>
-    <col min="31" max="31" width="39.140625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="45.28515625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="39.1796875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="45.26953125" style="1" customWidth="1"/>
     <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3963,7 +3972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4017,7 +4026,7 @@
       </c>
       <c r="AB2" s="12"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4056,7 +4065,7 @@
       </c>
       <c r="AB3" s="12"/>
     </row>
-    <row r="4" spans="1:32" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" ht="87" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4100,7 +4109,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4139,7 +4148,7 @@
       </c>
       <c r="AB5" s="12"/>
     </row>
-    <row r="6" spans="1:32" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -4206,7 +4215,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -4259,7 +4268,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -4321,7 +4330,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="165" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="145" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4380,7 +4389,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="135" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -4436,7 +4445,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4504,7 +4513,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4572,7 +4581,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4634,7 +4643,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4702,7 +4711,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4764,7 +4773,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4826,7 +4835,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -4888,7 +4897,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -4950,7 +4959,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" ht="87" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -5018,7 +5027,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -5074,7 +5083,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" ht="87" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -5139,7 +5148,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -5198,7 +5207,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="180" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="174" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -5254,7 +5263,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="87" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -5316,7 +5325,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -5369,7 +5378,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -5410,7 +5419,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" ht="87" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -5472,7 +5481,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="87" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -5531,7 +5540,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -5593,7 +5602,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5652,7 +5661,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="165" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5714,7 +5723,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5776,7 +5785,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5838,7 +5847,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5876,7 +5885,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="195" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5914,7 +5923,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="116" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -5982,7 +5991,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" ht="116" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -6050,7 +6059,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -6118,7 +6127,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -6162,7 +6171,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -6225,7 +6234,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -6263,7 +6272,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -6301,7 +6310,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -6360,7 +6369,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -6419,7 +6428,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -6478,7 +6487,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="120" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" ht="87" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -6543,7 +6552,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -6602,7 +6611,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -6648,20 +6657,23 @@
       <c r="T48" s="1" t="s">
         <v>611</v>
       </c>
+      <c r="U48" s="12" t="s">
+        <v>905</v>
+      </c>
       <c r="V48" s="1" t="s">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="X48" s="11" t="s">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="Y48" s="11" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -6702,7 +6714,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -6740,7 +6752,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -6781,7 +6793,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -6822,7 +6834,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -6860,7 +6872,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="225" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" ht="203" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -6929,7 +6941,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -6967,7 +6979,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -7032,7 +7044,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -7098,7 +7110,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="90" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -7166,7 +7178,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -7219,7 +7231,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="165" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -7278,7 +7290,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -7316,7 +7328,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -7381,7 +7393,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -7440,7 +7452,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -7499,7 +7511,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="180" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -7561,7 +7573,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -7602,7 +7614,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -7667,7 +7679,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="255" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="232" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -7730,7 +7742,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="255" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="232" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -7789,7 +7801,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="58" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -7854,7 +7866,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -7913,7 +7925,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="87" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -7985,7 +7997,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="120" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="87" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -8050,7 +8062,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="405" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -8118,7 +8130,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -8156,7 +8168,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -8194,7 +8206,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -8247,7 +8259,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="210" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -8309,7 +8321,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="145" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -8374,7 +8386,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="145" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -8433,7 +8445,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -8477,7 +8489,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -8536,7 +8548,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -8595,7 +8607,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="84" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -8654,7 +8666,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="85" spans="1:28" ht="195" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" ht="174" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -8713,7 +8725,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="86" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -8781,7 +8793,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="87" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -8846,7 +8858,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="88" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -8905,7 +8917,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="89" spans="1:28" ht="60" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" ht="58" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -8958,7 +8970,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="90" spans="1:28" ht="105" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -9014,7 +9026,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="91" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -9076,7 +9088,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="92" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -9138,7 +9150,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="93" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -9200,7 +9212,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="94" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -9262,7 +9274,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="95" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -9288,23 +9300,23 @@
         <v>466</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>477</v>
+        <v>906</v>
       </c>
       <c r="V95" s="1" t="s">
-        <v>513</v>
+        <v>474</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>546</v>
+        <v>500</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>513</v>
+        <v>907</v>
       </c>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -9346,7 +9358,7 @@
       </c>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -9388,7 +9400,7 @@
       </c>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -9450,7 +9462,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="99" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -9515,7 +9527,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="100" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -9577,7 +9589,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="101" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -9639,7 +9651,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -9681,7 +9693,7 @@
       </c>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -9743,7 +9755,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -9787,7 +9799,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -9831,7 +9843,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -9875,7 +9887,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="107" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -9919,7 +9931,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="108" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -9976,7 +9988,7 @@
       </c>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:28" ht="285" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -10033,7 +10045,7 @@
       </c>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -10089,7 +10101,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -10145,7 +10157,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="112" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -10201,7 +10213,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -10260,7 +10272,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -10325,7 +10337,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="150" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" ht="145" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -10390,7 +10402,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -10428,7 +10440,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -10466,7 +10478,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -10504,7 +10516,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -10542,7 +10554,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -10580,7 +10592,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -10618,7 +10630,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>121</v>
       </c>

--- a/baseline/data_processing_elements-NES.xlsx
+++ b/baseline/data_processing_elements-NES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maelstrom\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EC0DDE-2EDE-4B67-858B-6C9F0B0A8E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA726EF-D272-4874-9852-F0D7C7A0344C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="914">
   <si>
     <t>index</t>
   </si>
@@ -3355,12 +3355,39 @@
     <t>The threshold of the machine used for analysis was 4 which is too high to get a proper distribution.</t>
   </si>
   <si>
-    <t>cancer_kidney</t>
+    <t>cancer_type_throat</t>
   </si>
   <si>
     <t>case_when(
 fq113 == 2 ~ 0L;
-cancer_kidney == 1 ~ 1L;
+cancer_type_throat == 1 ~ 1L;
+ELSE ~ NA_integer_ )</t>
+  </si>
+  <si>
+    <t>case_when(
+fq113 == 2 ~ 0L;
+cancer_type_kidney == 1 ~ 1L;
+ELSE ~ NA_integer_ )</t>
+  </si>
+  <si>
+    <t>cancer_type_kidney</t>
+  </si>
+  <si>
+    <t>cancer_type_leukaemia</t>
+  </si>
+  <si>
+    <t>case_when(
+fq113 == 2 ~ 0L;
+cancer_type_leukaemia == 1 ~ 1L;
+ELSE ~ NA_integer_ )</t>
+  </si>
+  <si>
+    <t>cancer_type_uterus</t>
+  </si>
+  <si>
+    <t>case_when(
+fq113 == 2 ~ 0L;
+cancer_type_uterus == 1 ~ 1L;
 ELSE ~ NA_integer_ )</t>
   </si>
 </sst>
@@ -9300,7 +9327,7 @@
         <v>466</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="V95" s="1" t="s">
         <v>474</v>
@@ -9312,7 +9339,7 @@
         <v>526</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="Z95" s="2"/>
     </row>
@@ -9342,19 +9369,19 @@
         <v>466</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>477</v>
+        <v>906</v>
       </c>
       <c r="V96" s="1" t="s">
-        <v>513</v>
+        <v>474</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>546</v>
+        <v>500</v>
       </c>
       <c r="X96" s="1" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>513</v>
+        <v>907</v>
       </c>
       <c r="Z96" s="2"/>
     </row>
@@ -9384,19 +9411,19 @@
         <v>466</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>477</v>
+        <v>910</v>
       </c>
       <c r="V97" s="1" t="s">
-        <v>513</v>
+        <v>474</v>
       </c>
       <c r="W97" s="1" t="s">
-        <v>546</v>
+        <v>500</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>513</v>
+        <v>911</v>
       </c>
       <c r="Z97" s="2"/>
     </row>
@@ -9746,7 +9773,7 @@
         <v>526</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>831</v>
+        <v>913</v>
       </c>
       <c r="Z103" s="2" t="s">
         <v>727</v>
@@ -9781,19 +9808,19 @@
         <v>466</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>477</v>
+        <v>912</v>
       </c>
       <c r="V104" s="1" t="s">
-        <v>513</v>
+        <v>474</v>
       </c>
       <c r="W104" s="1" t="s">
-        <v>546</v>
+        <v>500</v>
       </c>
       <c r="X104" s="1" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="Y104" s="2" t="s">
-        <v>513</v>
+        <v>831</v>
       </c>
       <c r="Z104" s="2" t="s">
         <v>736</v>

--- a/baseline/data_processing_elements-NES.xlsx
+++ b/baseline/data_processing_elements-NES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maelstrom\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA726EF-D272-4874-9852-F0D7C7A0344C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94A739F-3AA6-4FC5-AB27-E5EFEB875E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
   </bookViews>
@@ -3291,17 +3291,8 @@
 ELSE ~ NA_integer_)</t>
   </si>
   <si>
-    <t>case_when(
-fq289 == 1 | fq319 == 1 | fq364 == 1 ~ 1L;
-fq289 == 2 &amp; fq319 == 2 &amp; fq364 ==0 ~ 0L ; 
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
     <t>questionnaire_date;
 bq2</t>
-  </si>
-  <si>
-    <t>lubridate::interval(as.Date(questionnaire_date), as.Date(bq2)) %/% lubridate::years(1)</t>
   </si>
   <si>
     <t>as.numeric(e32)</t>
@@ -3389,6 +3380,15 @@
 fq113 == 2 ~ 0L;
 cancer_type_uterus == 1 ~ 1L;
 ELSE ~ NA_integer_ )</t>
+  </si>
+  <si>
+    <t>case_when(
+fq289 == 1 | fq319 == 1 | fq364 == 1 ~ 1L;
+fq289 == 2 &amp; fq319 == 2 &amp; fq364 ==2 ~ 0L ; 
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>lubridate::interval(as.Date(bq2),as.Date(questionnaire_date)) %/% lubridate::years(1)</t>
   </si>
 </sst>
 </file>
@@ -4321,7 +4321,7 @@
         <v>396</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>494</v>
@@ -4351,7 +4351,7 @@
         <v>486</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>890</v>
+        <v>913</v>
       </c>
       <c r="AB8" s="12" t="s">
         <v>778</v>
@@ -5228,7 +5228,7 @@
         <v>486</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="AB22" s="12" t="s">
         <v>870</v>
@@ -5502,7 +5502,7 @@
         <v>486</v>
       </c>
       <c r="Y27" s="12" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="AB27" s="12" t="s">
         <v>792</v>
@@ -5623,7 +5623,7 @@
         <v>486</v>
       </c>
       <c r="Y29" s="11" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="AB29" s="12" t="s">
         <v>795</v>
@@ -5682,7 +5682,7 @@
         <v>526</v>
       </c>
       <c r="Y30" s="12" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="AB30" s="12" t="s">
         <v>794</v>
@@ -5744,7 +5744,7 @@
         <v>486</v>
       </c>
       <c r="Y31" s="12" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="AB31" s="12" t="s">
         <v>796</v>
@@ -5806,7 +5806,7 @@
         <v>486</v>
       </c>
       <c r="Y32" s="12" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="AB32" s="12" t="s">
         <v>795</v>
@@ -5865,7 +5865,7 @@
         <v>526</v>
       </c>
       <c r="Y33" s="12" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>564</v>
@@ -5909,7 +5909,7 @@
         <v>486</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="159.5" x14ac:dyDescent="0.35">
@@ -5944,7 +5944,7 @@
         <v>526</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>885</v>
@@ -6145,7 +6145,7 @@
         <v>486</v>
       </c>
       <c r="Y38" s="12" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>569</v>
@@ -6390,7 +6390,7 @@
         <v>486</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="AB43" s="12" t="s">
         <v>850</v>
@@ -6449,7 +6449,7 @@
         <v>486</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="AB44" s="12" t="s">
         <v>850</v>
@@ -6508,7 +6508,7 @@
         <v>486</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="AB45" s="12" t="s">
         <v>850</v>
@@ -6632,7 +6632,7 @@
         <v>486</v>
       </c>
       <c r="Y47" s="11" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="AB47" s="12" t="s">
         <v>850</v>
@@ -6685,7 +6685,7 @@
         <v>611</v>
       </c>
       <c r="U48" s="12" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="V48" s="1" t="s">
         <v>513</v>
@@ -8879,7 +8879,7 @@
         <v>526</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="AB87" s="12" t="s">
         <v>819</v>
@@ -9327,7 +9327,7 @@
         <v>466</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="V95" s="1" t="s">
         <v>474</v>
@@ -9339,7 +9339,7 @@
         <v>526</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="Z95" s="2"/>
     </row>
@@ -9369,7 +9369,7 @@
         <v>466</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="V96" s="1" t="s">
         <v>474</v>
@@ -9381,7 +9381,7 @@
         <v>526</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="Z96" s="2"/>
     </row>
@@ -9411,7 +9411,7 @@
         <v>466</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="V97" s="1" t="s">
         <v>474</v>
@@ -9423,7 +9423,7 @@
         <v>526</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="Z97" s="2"/>
     </row>
@@ -9773,7 +9773,7 @@
         <v>526</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="Z103" s="2" t="s">
         <v>727</v>
@@ -9808,7 +9808,7 @@
         <v>466</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="V104" s="1" t="s">
         <v>474</v>

--- a/baseline/data_processing_elements-NES.xlsx
+++ b/baseline/data_processing_elements-NES.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maelstrom\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94A739F-3AA6-4FC5-AB27-E5EFEB875E93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A0385C-A6E2-485F-A499-C9768AB9458D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{0073E314-1B2C-4924-AC81-D526EEC9786A}"/>
   </bookViews>
   <sheets>
     <sheet name="DPE" sheetId="1" r:id="rId1"/>
@@ -3331,9 +3331,6 @@
 ELSE ~ NA)</t>
   </si>
   <si>
-    <t>(as.numeric(e9) + as.numeric(e13) + as.numeric(e17) + as.numeric(e21)) %&gt;% round(., 0)</t>
-  </si>
-  <si>
     <t>as.numeric(e29)</t>
   </si>
   <si>
@@ -3389,6 +3386,15 @@
   </si>
   <si>
     <t>lubridate::interval(as.Date(bq2),as.Date(questionnaire_date)) %/% lubridate::years(1)</t>
+  </si>
+  <si>
+    <t>round(rowMeans(
+mutate(.,
+e9_temp = as.numeric(e9),
+e13_temp = as.numeric(e13),
+e17_temp = as.numeric(e17),
+e21_temp = as.numeric(e21)) %&gt;% 
+select(e9_temp, e13_temp, e17_temp, e21_temp), na.rm = TRUE), 0)</t>
   </si>
 </sst>
 </file>
@@ -3547,7 +3553,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3864,44 +3870,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32FF9666-3C68-4610-B7F3-25EE531D7B07}">
   <dimension ref="A1:AF122"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="29" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.7265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.54296875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="40.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="14.54296875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="70.7265625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="28.1796875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="32.453125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="70.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="28.140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="32.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="42" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14.81640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="53.7265625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="3.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="4.54296875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="53.7109375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="3.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.5703125" style="1" customWidth="1"/>
     <col min="18" max="18" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="45.81640625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.26953125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="32.1796875" style="12" customWidth="1"/>
+    <col min="19" max="19" width="45.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.28515625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="32.140625" style="12" customWidth="1"/>
     <col min="22" max="22" width="15" style="1" customWidth="1"/>
-    <col min="23" max="23" width="15.453125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="16.1796875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="49.7265625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="42.26953125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="46.453125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="54.1796875" style="14" customWidth="1"/>
-    <col min="29" max="29" width="39.1796875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="15.42578125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="16.140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="49.7109375" style="2" customWidth="1"/>
+    <col min="26" max="26" width="42.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="46.42578125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="54.140625" style="14" customWidth="1"/>
+    <col min="29" max="29" width="39.140625" style="1" customWidth="1"/>
     <col min="30" max="30" width="29" style="1" customWidth="1"/>
-    <col min="31" max="31" width="39.1796875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="45.26953125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="39.140625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="45.28515625" style="1" customWidth="1"/>
     <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3999,7 +4005,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4053,7 +4059,7 @@
       </c>
       <c r="AB2" s="12"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4092,7 +4098,7 @@
       </c>
       <c r="AB3" s="12"/>
     </row>
-    <row r="4" spans="1:32" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4136,7 +4142,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4175,7 +4181,7 @@
       </c>
       <c r="AB5" s="12"/>
     </row>
-    <row r="6" spans="1:32" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -4242,7 +4248,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -4295,7 +4301,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -4351,13 +4357,13 @@
         <v>486</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="AB8" s="12" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="145" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -4416,7 +4422,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" ht="135" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -4472,7 +4478,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -4540,7 +4546,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -4608,7 +4614,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -4670,7 +4676,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="14" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -4738,7 +4744,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -4800,7 +4806,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -4862,7 +4868,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -4924,7 +4930,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -4986,7 +4992,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="87" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -5054,7 +5060,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -5110,7 +5116,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="87" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -5175,7 +5181,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -5234,7 +5240,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="174" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:28" ht="180" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -5290,7 +5296,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="87" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -5352,7 +5358,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -5405,7 +5411,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -5446,7 +5452,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="87" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -5508,7 +5514,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="87" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -5567,7 +5573,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="58" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -5629,7 +5635,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="58" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -5688,7 +5694,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -5750,7 +5756,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -5812,7 +5818,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -5874,7 +5880,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -5912,7 +5918,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:28" ht="195" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -5950,7 +5956,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="116" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -6018,7 +6024,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="116" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -6086,7 +6092,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -6145,7 +6151,7 @@
         <v>486</v>
       </c>
       <c r="Y38" s="12" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>569</v>
@@ -6154,7 +6160,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="58" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -6198,7 +6204,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -6261,7 +6267,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -6299,7 +6305,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -6337,7 +6343,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -6390,13 +6396,13 @@
         <v>486</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AB43" s="12" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -6449,13 +6455,13 @@
         <v>486</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="AB44" s="12" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -6508,13 +6514,13 @@
         <v>486</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="AB45" s="12" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="87" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:28" ht="120" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -6579,7 +6585,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -6638,7 +6644,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -6685,7 +6691,7 @@
         <v>611</v>
       </c>
       <c r="U48" s="12" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="V48" s="1" t="s">
         <v>513</v>
@@ -6700,7 +6706,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -6741,7 +6747,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -6779,7 +6785,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -6820,7 +6826,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -6861,7 +6867,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -6899,7 +6905,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="203" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:28" ht="225" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -6968,7 +6974,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="58" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -7006,7 +7012,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:28" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -7071,7 +7077,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -7137,7 +7143,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:28" ht="90" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -7205,7 +7211,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -7258,7 +7264,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:28" ht="165" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -7317,7 +7323,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -7355,7 +7361,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:28" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -7420,7 +7426,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -7479,7 +7485,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -7538,7 +7544,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:29" ht="180" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -7600,7 +7606,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -7641,7 +7647,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -7706,7 +7712,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="232" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:29" ht="255" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -7769,7 +7775,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="232" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:29" ht="255" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -7828,7 +7834,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="58" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:29" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -7893,7 +7899,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:29" ht="105" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -7952,7 +7958,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="87" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -8024,7 +8030,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="87" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:29" ht="120" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -8089,7 +8095,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:29" ht="405" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -8157,7 +8163,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -8195,7 +8201,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -8233,7 +8239,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="87" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:29" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -8286,7 +8292,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="188.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:29" ht="210" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -8348,7 +8354,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="145" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:29" ht="150" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -8413,7 +8419,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="145" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:29" ht="150" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -8472,7 +8478,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="81" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -8516,7 +8522,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="82" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -8575,7 +8581,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="83" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -8634,7 +8640,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="84" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -8693,7 +8699,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="85" spans="1:28" ht="174" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:28" ht="180" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -8752,7 +8758,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="86" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -8820,7 +8826,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="87" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -8879,13 +8885,13 @@
         <v>526</v>
       </c>
       <c r="Y87" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AB87" s="12" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="88" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -8944,7 +8950,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="89" spans="1:28" ht="58" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:28" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -8997,7 +9003,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="90" spans="1:28" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:28" ht="105" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -9053,7 +9059,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="91" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -9115,7 +9121,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="92" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -9177,7 +9183,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="93" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -9239,7 +9245,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="94" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -9301,7 +9307,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="95" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -9327,7 +9333,7 @@
         <v>466</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V95" s="1" t="s">
         <v>474</v>
@@ -9339,11 +9345,11 @@
         <v>526</v>
       </c>
       <c r="Y95" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -9369,7 +9375,7 @@
         <v>466</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V96" s="1" t="s">
         <v>474</v>
@@ -9381,11 +9387,11 @@
         <v>526</v>
       </c>
       <c r="Y96" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -9411,7 +9417,7 @@
         <v>466</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="V97" s="1" t="s">
         <v>474</v>
@@ -9423,11 +9429,11 @@
         <v>526</v>
       </c>
       <c r="Y97" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -9489,7 +9495,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="99" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -9554,7 +9560,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="100" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -9616,7 +9622,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="101" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -9678,7 +9684,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="102" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -9720,7 +9726,7 @@
       </c>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -9773,7 +9779,7 @@
         <v>526</v>
       </c>
       <c r="Y103" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="Z103" s="2" t="s">
         <v>727</v>
@@ -9782,7 +9788,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="104" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -9808,7 +9814,7 @@
         <v>466</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="V104" s="1" t="s">
         <v>474</v>
@@ -9826,7 +9832,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="105" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -9870,7 +9876,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="106" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -9914,7 +9920,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="107" spans="1:28" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -9958,7 +9964,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="108" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -10015,7 +10021,7 @@
       </c>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:28" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:28" ht="285" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -10072,7 +10078,7 @@
       </c>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -10128,7 +10134,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="111" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -10184,7 +10190,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="112" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -10240,7 +10246,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -10299,7 +10305,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -10364,7 +10370,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="145" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:28" ht="150" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -10429,7 +10435,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -10467,7 +10473,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:28" ht="45" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -10505,7 +10511,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -10543,7 +10549,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -10581,7 +10587,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -10619,7 +10625,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -10657,7 +10663,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
